--- a/mitacs_proyectos_ciudades_pastel.xlsx
+++ b/mitacs_proyectos_ciudades_pastel.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -56,7 +68,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -64,19 +76,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,901 +479,901 @@
   <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Keyword Usada</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ID Proyecto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Universidad</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Campus</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Idioma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>51360</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Robust Aggregation for Multi-Node LLM Inference</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>As large language models are increasingly deployed in distributed and multi-party settings, ensuring the reliability and integrity of their outputs becomes a critical challenge. In such settings, a single model instance may not be sufficient to guarantee trustworthy responses which could be due to resource constraints, fault tolerance requirements, or the need for redundancy. Distributed LLM inference, where multiple model instances collaborate to produce a final output, offers a promising direction, but introduces new challenges around consistency, coordination, and adversarial robustness. This project investigates robust aggregation mechanisms for distributed LLM inference in the presence of adversarial or unreliable nodes. In a multi-node inference setting, responses from multiple LLM instances must be aggregated into a single reliable output. This process that becomes challenging when some nodes behave maliciously, are compromised, or return inconsistent results, degrading overall system trustworthiness. The goal is to design and evaluate an aggregation layer that improves the reliability and robustness of distributed inference. This involves exploring strategies to detect inconsistent or outlier responses and select or synthesize outputs that reflect consensus across nodes. The work involves understanding how different aggregation approaches perform under varying levels of adversarial pressure, and what trade-offs emerge between robustness, accuracy, and computational overhead. The project will also examine whether aggregation strategies can be made adaptive, adjusting their behavior based on observed node reliability over time. The system will be evaluated under a range of adversarial scenarios, including random incorrect outputs, coordinated malicious responses, and subtle misinformation attacks. Beyond adversarial robustness, the project will also consider practical deployment constraints such as latency and scalability, ensuring that the proposed mechanisms remain viable in real-world distributed settings. Key evaluation metrics will include response accuracy, attack resilience, latency, and system efficiency.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>51375</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Agentic Security Analysis for Detecting and Mitigating Fraudulent Cross-Chain Messaging</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Agentic Security Analysis for Detecting and Mitigating Fraudulent Cross-Chain Messaging</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>51430</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Monitoring and Analyzing Cross-Layer Messaging in Blockchain Layer 2 Architectures</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Monitoring and Analyzing Cross-Layer Messaging in Blockchain Layer 2 Architectures</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>52201</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Implementation of Lightweight Semantic Communication Models for Intelligent IoT Systems</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Implementation of Lightweight Semantic Communication Models for Intelligent IoT Systems</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>52202</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>AI-Assisted Wireless Link Selection for Reliable IoT and V2X Networks</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>This project investigates AI-assisted wireless link selection for reliable IoT and vehicle-to-everything (V2X) networks. In many wireless systems, devices must decide which communication link, relay, access point, or neighbouring node should be used to transmit data. Poor link selection may increase packet loss, delay, and information staleness, especially when devices are mobile or when channel conditions change over time. The student will develop a Python-based simulation framework for a simplified IoT or V2X network. Nodes may represent sensors, vehicles, roadside units, or access points. The simulator will model basic wireless link quality using distance, path loss, noise, interference, or random channel variation. The student will implement and compare several link-selection strategies, including shortest-distance selection, strongest-signal selection, random selection, and simple machine-learning-based prediction. The project will evaluate performance using metrics such as packet success rate, delay, link reliability, number of failed transmissions, and possibly Age of Information. The emphasis is on implementation, experimentation, and visualization rather than advanced wireless theory. The expected outcomes include well-documented simulation code, performance plots, and a short technical report explaining which link-selection strategies work best under different network conditions. This project is suitable for students interested in wireless networks, IoT, vehicular communications, machine learning, simulation, and data analysis.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>52203</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Implementation of Trust-Aware Security Mechanisms for IoT and Vehicular Edge Networks</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Implementation of Trust-Aware Security Mechanisms for IoT and Vehicular Edge Networks</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>52204</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Graph-Based Simulation of Freshness-Aware Resource Allocation in Edge-IoT Networks</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Graph-Based Simulation of Freshness-Aware Resource Allocation in Edge-IoT Networks</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>52538</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Reliability-Aware Workload Generation for LLM Serving Systems</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>51257</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Visual Motion Analysis from Images and Videos</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>University of Alberta</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>This project focuses on analyzing visual behaviors of articulated objects (human and animals) from video feed, a problem that plays a crucial role in many real-life applications ranging from natural user interface to autonomous driving. As a member of the Vision and Learning Lab at the University of Alberta (https://vision-and-learning-lab-ualberta.github.io/), you are expected to work with a graduate student/Postdoc researcher, get familiar with state-of-the-art deep learning, quantum machine learning and computer vision techniques, and gain hands-on research experience on benchmark and home-grown datasets. There are ample opportunities to be involved in exciting research topics in computer vision and to publish</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>51942</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Student engagement detection in online learning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Online learning plays a key role in today’s education system. Engagement detection in online learning is crucial as the student’s success in online courses heavily depends on his/her state of mind. In this paper, we will use student’s behavioral, emotional, and cognitive dimensions for engagement detection. Different machine learning and deep learning approaches will be used to analyze facial expressions and forum posts in online courses. We will perform empirical studies and develop prototype applications to test and explore theoretical concepts on student engagement detection in online learning platform.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>51943</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Visualization of educational data in online learning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Educational institutions capture huge amounts of educational data, especially in online learning. Data mining techniques have shown promises to interpret these data using different patterns. However, understanding the mining patterns and extracting meaningful information from the data require reasonable skills and knowledge for the users. Information visualization, due to its potential to display large amount of data, may fill this gap. In this research project, we will analyze various visualization techniques to represent meaningful information from the educational data, especially dealing with monitoring student performance, understanding learning style, analyzing course and program status, and dropout prediction. We will develop a learner- or instructor-focused effective visualization system for online learning environment.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>51944</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Early dropout prediction in e-learning courses using machine learning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>High dropout rate is a major concern for many universities that offer online courses. If the dropout-prone students can be identified at their early stages of learning, the dropout rate can be reduced by providing individualized support to the students at-risk. Due to the electronic nature of the learning management systems (LMS), various attributes of the students’ progress can be monitored and analyzed over time. The main objective of this project is to explore what progress information about a student can be used from LMS and how this information can be used with a classification model to predict the students at risk. Different machine learning and deep learning methods will be investigated for early dropout prediction in this research project.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>51945</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Pedagogical Intervention Design for Online Learners</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>Designing pedagogical interventions based on student's engagement detection is a challenging research problem. In this research, we will explore the use of engagement detection and learning analytics to automate personalized pedagogical support for online learners, specifically to answer the following questions: at what point and with what frequency should the students be consulted? why are they being consulted? what intervention should be provided? How will the pedagogical interventions integrate with the rest of the teaching and learning practices? We will investigate this area and develop a demo program on pedagogical intervention for the online learners.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>52076</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Applications of Artificial Intelligence and Reinforcement Learning in Assessment of Thyroid Nodule Using Ultrasound</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>University of Alberta</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Applications of Artificial Intelligence and Reinforcement Learning in Assessment of Thyroid Nodule Using Ultrasound</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>52255</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Secure Retrieval-Augmented Generation Against Poisoning Attacks</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Concordia University of Edmonton</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>Retrieval-Augmented Generation (RAG) systems enhance large language models (LLMs) by integrating external knowledge retrieval into the generation process. While RAG improves factual accuracy and domain adaptability, its dependence on external knowledge sources introduces serious security vulnerabilities, particularly poisoning attacks. In these attacks, adversaries inject malicious or misleading documents into the knowledge base so that the retriever selects poisoned content during inference, causing the LLM to generate manipulated, biased, or harmful responses. Such vulnerabilities pose significant risks for real-world applications in healthcare, finance, education, and cybersecurity. This research project aims to develop a secure and robust RAG framework capable of detecting and mitigating retrieval-layer poisoning attacks. The project will investigate how poisoned documents affect retrieval rankings, embedding representations, and downstream text generation in modern RAG architectures. Various attack strategies, including semantic poisoning, adversarial document injection, stealthy trigger-based attacks, and retrieval manipulation techniques, will be explored to understand their impact on system reliability and trustworthiness. To improve RAG security, the research will examine defense mechanisms such as anomaly detection, secure reranking, retrieval filtering, embedding consistency verification, and trust-aware retrieval strategies. Privacy-preserving techniques and robust retrieval optimization methods will also be investigated to reduce the influence of malicious content while maintaining retrieval quality and generation accuracy. The expected outcome of this research is a scalable and attack-resilient RAG framework that enhances the security, reliability, and trustworthiness of LLM-based systems operating in adversarial environments. The proposed framework will contribute toward the safe deployment of AI-driven knowledge systems in critical real-world applications.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>52296</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>A deep normative model of the human brain from MRI data</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>MacEwan University</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>The project involves analysis brain MRI data. In neuroimaging is important to understand how brain structures are changing due to normal ageing or disease. The goal of this project is to generate a model of the ageing human brain and relate disease populations to this model. We will work with medical data provided by our collaboration between the Computing Science Department and the Department of Neurology, at University of Alberta. Preliminary work from our group [1,2] has been done to create a shape model of the healthy hippocampus. The model uses a variational graph convolutional autoencoder conditioned by age. The proposed project extends this model to study full brain atrophy and cortical thickness variability. The focus for next summer is to create a normative model of healthy brain surface from a large collection of MRI images (ex UKBiobank). Disease-related abnormalities will be defined as deviations from this model. For the diseased population we will use internal data (ALS patients) and ADNI data (AD patients). The results of this project will be interpreted by our medical collaborators and summarized in a publication. [1] Kiechle J., Miller D., Slessor J., Pietrosanu M., Beaulieu C., Cobzas D. (2023). Explaining anatomical shape variability International Symposium on Biomedical Imaging 2023 [2] Rabbi J., Kiechle J., Beaulieu C., Ray N., Cobzas D. (2024) Disentangling Hippocampal Shape Variations, MELBA journal, November 2024</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>52390</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Agentic Federated Learning for Adaptive IoT Intrusion Detection</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Concordia University of Edmonton</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H18" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>Agentic Federated Learning for Adaptive IoT Intrusion Detection proposes an intelligent and privacy-preserving cybersecurity framework for detecting malicious activities in heterogeneous Internet of Things (IoT) environments. The project integrates Federated Learning (FL) with autonomous AI agents to enable adaptive, scalable, and communication-efficient intrusion detection across distributed IoT devices without requiring the sharing of raw data. Inspired by recent advances in Agentic Federated Learning, the framework leverages specialized collaborative agents to automate the design, optimization, and deployment of FL-based intrusion detection strategies. Traditional FL-based intrusion detection systems often rely on static configurations and predefined aggregation mechanisms, making them vulnerable to evolving cyberattacks, device heterogeneity, non-IID traffic distributions, and communication constraints commonly observed in IoT ecosystems. To address these limitations, the proposed framework introduces multiple intelligent agents responsible for planning, optimization, threat analysis, communication management, and adaptive response generation. These agents continuously monitor network conditions and dynamically adjust federated training strategies, client participation, and defense mechanisms to improve detection performance and system robustness. The proposed architecture follows a multi-stage workflow consisting of planning, programming, optimization, and deployment phases, similar to the human software engineering lifecycle. A planning agent identifies suitable FL configurations and security requirements, while coding and optimization agents iteratively refine intrusion detection models using simulated IoT attack scenarios. Deployment agents further adapt the optimized framework for practical FL platforms such as Flower or FedML. The research aims to develop an adaptive and autonomous intrusion detection framework capable of mitigating sophisticated cyber threats such as distributed denial-of-service (DDoS), botnet attacks, and poisoning attacks in decentralized IoT networks. The proposed system is expected to improve detection accuracy, communication efficiency, privacy preservation, and resilience against adversarial behaviors in real-world IoT deployments.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>52391</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Agentic Multimodal Fake News Detection</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Concordia University of Edmonton</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H19" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Agentic Multimodal Fake News Detection proposes an intelligent framework for identifying and mitigating misinformation by integrating multimodal learning with autonomous AI agents. The project aims to detect fake news by jointly analyzing multiple information sources, including textual content, images, audio, video, social context, and metadata, while enabling adaptive reasoning and evidence verification through collaborative agent-based decision-making. Traditional fake news detection systems primarily rely on static classification models that process textual or visual information independently. However, modern misinformation campaigns frequently combine manipulated images, misleading captions, synthetic audio, AI-generated videos, fabricated social interactions, and coordinated dissemination strategies, making single-modal and fixed detection approaches insufficient. Furthermore, existing systems often lack reasoning capability, explainability, and the ability to dynamically verify information using external knowledge sources. Inspired by recent advances in agentic AI systems and multi-agent collaboration, the proposed framework introduces specialized autonomous agents responsible for different analytical tasks. A text analysis agent examines linguistic patterns, semantic inconsistencies, and misleading narratives, while visual analysis agents identify manipulated or out-of-context images and videos. Additional agents analyze synthetic or manipulated audio, social propagation behavior, user interaction patterns, and metadata anomalies to assess the credibility and origin of content. Evidence retrieval and fact-verification agents further leverage Retrieval-Augmented Generation (RAG), large language models (LLMs), and multimodal transformers to validate claims using trusted external knowledge sources. These agents collaboratively interact through an adaptive workflow that continuously refines detection decisions based on contextual and multimodal evidence, improving explainability, robustness, and adaptability against emerging misinformation strategies, including AI-generated fake media and coordinated disinformation campaigns. This research contributes toward the development of trustworthy and intelligent misinformation detection systems capable of supporting digital media platforms, public information services, and online social networks in combating the rapid spread of fake news.</t>
         </is>
@@ -1353,42 +1385,42 @@
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>52868</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>EN: Toward Sustainable AI - Assessing and Reducing the Environmental Footprint of AI Models // FR: Vers une IA durable - Évaluation et réduction de l’empreinte environnementale des modèles d’IA</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Royal Military College of Canada</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Kingston</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Kingston, Ontario</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>EN: Toward Sustainable AI - Assessing and Reducing the Environmental Footprint of AI Models // FR: Vers une IA durable - Évaluation et réduction de l’empreinte environnementale des modèles d’IA</t>
         </is>
@@ -1400,42 +1432,42 @@
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>51768</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Deep learning for integrating multimodal data for precision medicine</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Western University</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>London, Ontario</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Omics data refers to the high-dimensional and highly correlated data from genomics, transcriptomics, microbiome, metabolomics, and proteomics. Different computational and statistical analyses of these data can be used to identify risk factors for different diseases or to build autonomous disease prediction models. Analysis of omics data, imaging, and medical health records has become very popular in disease studies because such analysis is helpful to predict whether a patient has a certain disease or not. It is expected that integration of knowledge from multiple data sources measured on the same individuals should improve the prediction performance of patients with chronic diseases. Because one of these data sources may have biological knowledge that is absent in another one. However, due to the high-dimensional nature of the data sets with hundreds of thousands of variables and very small numbers of samples, traditional machine learning approaches (e.g. Support Vector Machines) have limitations to analyze these data efficiently. To overcome these limitations, the project will apply deep learning algorithms to learn knowledge from multiple data sources (omics, imaging, medical health records, etc.) at different feature levels, which will be used to predict disease outcomes and potential drug targets for the diseases. Specifically, the project will have these two objectives: 1) Apply deep learning algorithms to learn knowledge across data sources at a single feature level. 2) Apply transfer learning algorithms to learn knowledge across feature levels. Key Words: bioinformatics, computational biology, computer science, statistics, computing engineering, artificial intelligence, biostatistics, genome science, machine learning, algorithms, mathematics</t>
         </is>
@@ -1447,42 +1479,42 @@
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>51769</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Quantum equivariant diffusion model for 3D de novo molecule design</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Western University</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>London, Ontario</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Introduction Although state-of-the-art models such as equivariant diffusion models have achieved significant progress in generating realistic molecular structures, they still encounter limitations in handling the high-dimensional complexity and ensuring time efficiency. We hypothesize that quantum machine learning can potentially solve these problems. Therefore, we propose a Quantum Equivariant Diffusion Model (QEDM) for 3D de novo molecule design, which aims to enhance the quality of generated molecules while reducing both training and inference times. This innovative approach leverages the unique capabilities of quantum computing to overcome the inherent limitations of classical methods, promising substantial improvements in the efficiency and accuracy of molecular design. Research goal The overarching goal of this study is to build a QEDM to generate 3D de novo molecules with desired properties. Proposed analysis We will build our QEDM on the quantum platform (https://quantum.ibm.com/) provided by International Business Machines corporation (IBM). The QEDM will leverage a two-step process: a forward diffusion process and a backward denoising process. In the forward process, we will employ a non-unitary depolarizing channel to progressively add noise to the quantum-encoded representation of a molecular structure, transforming it into a maximally mixed state. Each molecule is initially represented by its atomic coordinates and types, which will be encoded into quantum states using amplitude encoding. The noise schedule will be designed using a cosine function to ensure a gradual and controlled transformation. For the backward process, we will implement a parameter-sharing quantum circuit that denoises the quantum states. This circuit will include a timestep embedding circuit to incorporate temporal information and a denoising circuit that processes the noisy quantum state along with the timestep embedding state. The quantum circuits will be designed with gates that implement rotations and translations consistent with the physical symmetries of the molecule, ensuring equivariance. Key Words: Physics, computational biology, computer</t>
         </is>
@@ -1494,42 +1526,42 @@
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>53116</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Text-Image Generalization Unlearnable Examples</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Western University</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>London, Ontario</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>While unlearnable examples have been actively studied for classification-oriented data protection, how to design effective unlearnable examples for text-image generative models remains underexplored. In this project, we will address several fundamental aspects of unlearnable visual protection for diffusion-based image editing. Ideally, the project will end up with a paper published at a top-tier ML/CV conference, such as CVPR, ICML, or NeurIPS. The key strengths/objectives of our project include: -- We will leverage the tools from representation learning and optimization principles to develop new theoretical and algorithmic insights for text-image generalization unlearnable examples. In other words, we will study how protected images can disrupt the correspondence between visual semantics and text-guided editing instructions, thereby motivating a principled protection framework for diffusion-based image editing. -- Our proposed framework will also support robustness against diverse editing requests, which are common in real-world text-image applications. For diffusion-based image editing, there exist several challenging scenarios: 1) instruction-dependent editing, where different text prompts may require modifying different semantic attributes, such as object appearance, background, style, or local structure; 2) model-dependent generation, where different diffusion models may rely on different visual-text representations and editing mechanisms. We will design principled methods to address these issues, so that protected images remain visually natural to humans but become difficult for diffusion models to correctly edit or exploit under diverse text-guided editing conditions.</t>
         </is>
@@ -1541,42 +1573,42 @@
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>53117</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Trustworthy AI for Data Privacy: Protecting Personal Data in the Era of Pretraining</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Western University</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>London, Ontario</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Trustworthy AI for Data Privacy: Protecting Personal Data in the Era of Pretraining</t>
         </is>
@@ -1588,42 +1620,42 @@
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>53118</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Foundation Prior-data Fitted Network Models for Scientific Discovery</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Western University</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>London, Ontario</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>This project aims to develop efficient foundation models for scientific discovery, with a focus on prior-data fitted networks (PFNs), in-context learning, and transfer learning. Many scientific problems in biology and biomedicine involve limited labeled data, heterogeneous measurements, expensive experiments, and distribution shifts across labs, patients, platforms, and experimental conditions. Standard deep learning methods often require task-specific training, extensive tuning, and large datasets, making them difficult to use in these data-limited scientific settings. PFN-style models offer a promising alternative: by learning from broad families of prior-generated tasks, they can make fast predictions on new datasets directly from context, without costly retraining. The project will pursue three connected objectives: -- We will design scientific priors and task-generation processes that capture useful structures in biological and biomedical data, such as tabular clinical variables, molecular features, perturbation responses, single-cell measurements, and multimodal embeddings. These priors will help encode realistic assumptions about noise, sparsity, causal structure, and cross-experiment variation. -- We will build efficient foundation model architectures that can transfer knowledge across datasets, tasks, and modalities while remaining computationally practical. This includes studying long-context prediction, uncertainty estimation, causal or treatment-effect prediction, and robustness under domain shift. -- We will evaluate the resulting models on real scientific prediction problems, such as biological response prediction, patient risk stratification, perturbation effect estimation, and data-limited biomedical decision support. The expected outcome is a new framework for building efficient, transferable, and reliable scientific foundation models. By reducing the need for repeated task-specific model training, this project aims to support faster hypothesis testing, better use of small scientific datasets, and more accessible AI tools for biology and biomedicine.</t>
         </is>
@@ -1635,42 +1667,42 @@
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>51900</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Accelerating Multi-Agent Learning Through Advisor-Guided Value Transfer</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Carleton University</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Accelerating Multi-Agent Learning Through Advisor-Guided Value Transfer</t>
         </is>
@@ -1682,42 +1714,42 @@
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>51901</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Learning to Adapt: Opponent-Aware Fine-Tuning of Decentralized Multi-Agent Policies</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Carleton University</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Learning to Adapt: Opponent-Aware Fine-Tuning of Decentralized Multi-Agent Policies</t>
         </is>
@@ -1729,465 +1761,465 @@
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>51902</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Multi-Agent Reinforcement Learning for Safe and Efficient Autonomous Driving in Dense Traffic Scenarios</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Carleton University</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>Multi-Agent Reinforcement Learning for Safe and Efficient Autonomous Driving in Dense Traffic Scenarios</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>51941</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Culturally Sensitive AI</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Université du Québec à Montréal</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>MONTREAL, Québec</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>During your internship, you will be involved in the development of machine/deep learning, sentiment analysis, speech transcription and information retrieval algorithms. Sub-field of artificial intelligence, machine learning studies and designs algorithms that learn from data to make predictions. You will apply your knowledge to tasks, questioning how AI-based systems could be designed to be culturally sensitive. You will have to handle large corpora of textual data to extract information, analyze their content, or discover embedded knowledge. You will explore various approaches (deep learning, genAI, etc.) to solve information extraction tasks, find relevant documents in a corpus, and classify documents (associate a category to a document), with a special focus on cultural adaptation. With our team, you will contribute to the development of automatic system that can, for instance, participate in evaluation campaigns like eRisk (https://early.irlab.org/) or CLPsych (http://clpsych.org/), or transcribe speech from languages spoken in various communities (see calame.tech).</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>51840</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Geometric Machine Learning and Interaction of Large Medical Image Datasets</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>École Polytechnique de Montréal</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Geometric Machine Learning and Interaction of Large Medical Image Datasets</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>51841</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Interactive Visualization and Manipulation of Modern Medical Images</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>École Polytechnique de Montréal</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>The complexity of modern medical imaging requires sophisticated visualization strategies. Through a combination of intelligent algorithms and advanced computer graphics, we reconstruct organs in 3D to ensure that physiological abnormalities can be efficiently identified. This internship focuses on developing a state-of-the-art visualization platform that integrates machine learning and image analysis. As a participant, you will master modern ML frameworks and innovative rendering techniques to build an interactive system capable of manipulating 3D and 4D (3D+t) datasets of the heart, brain, and other vital structures. As an intern, you will implement high-performance computer vision techniques to drive a robust retrieval and analysis system. You will join Team Polyshape at Polytechnique Montreal, a leading hub for engineering innovation. Our lab provides a vibrant, collaborative atmosphere with deep connections to premier research institutions across North America and Europe. Located in Montreal, you will experience a world-class cultural landscape in one of the most accessible and affordable major cities on the continent. Schedule and start dates remain flexible. Dates are flexible.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>51981</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Automated Software Modernization</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Concordia University</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>This research project focuses on developing automated approaches to modernizing legacy software systems using advanced software engineering and artificial intelligence techniques. Many existing systems rely on outdated architectures that limit scalability, security, and maintainability. The project aims to analyze legacy codebases, identify opportunities for refactoring, and transform monolithic applications into modular, cloud-native architectures. By leveraging tools for code analysis and machine learning-based pattern detection, the research will explore methods to reduce the complexity, cost, and risk associated with software modernization. The effectiveness of the proposed approaches will be evaluated using metrics such as performance, code quality, and system maintainability. The outcomes of this project are expected to contribute to more efficient and reliable modernization practices in both academic and industrial settings.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>52098</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Leveraging Large Language Models to Improve Software Development</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Concordia University</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>The research project focuses on the innovative application of large language models (LLMs) to assist in various aspects of software engineering. This project explores how LLMs can be integrated to improve software development processes, including but not limited to code generation, documentation, debugging, and testing. By leveraging the natural language understanding capabilities of LLMs, the project aims to provide tools that can interpret and generate human-like code comments, suggest code optimizations, and automate bug detection and resolution. This integration seeks to enhance developer productivity, reduce the complexity of software maintenance, and elevate overall code quality, ultimately contributing to more efficient and effective software development cycles.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>52508</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Computer Vision Methods for Surgical Navigation in Spine Surgery</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Université TÉLUQ</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>This project aims to develop an ultrasound-based surgical navigation solution to make spine surgery more accurate, safer, and more accessible. Each year, thousands of patients require spinal procedures involving the placement of pedicle screws to restore or maintain the biomechanical stability of the spine. However, inaccurate screw placement can lead to serious neurological, vascular, or mechanical complications. Current navigation approaches often rely on fluoroscopy or CT imaging, which can increase radiation exposure, require expensive equipment, and remain unavailable in many clinical settings. The goal of this project is to create and evaluate reliable ultrasound-based navigation methods that can support pedicle screw insertion during minimally invasive spine surgery. The project will combine ultrasound-to-3D model registration, automatic segmentation, adaptive planning, and real-time visualization of surgical instruments relative to patient anatomy. These methods will be integrated into an open-source surgical navigation platform, making the technology more accessible for research, training, and future clinical translation. A key scientific challenge will be to account for anatomical variability and biomechanical deformation during surgery, enabling robust registration between intraoperative ultrasound images and preoperative or patient-specific 3D models. The intern will contribute to the development, implementation, and evaluation of computer vision and image-guided surgery methods designed for realistic surgical conditions. The proposed approach will be quantitatively evaluated using ex vivo porcine spine models in minimally invasive pedicle screw insertion scenarios. Accuracy, robustness, repeatability, and usability will be assessed to determine the potential of the method as a radiation-free alternative to conventional navigation systems.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>52795</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>AI-Powered Autonomous Root Cause Analysis and Self-Healing Video Streaming Systems</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Concordia University</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>AI-Powered Autonomous Root Cause Analysis and Self-Healing Video Streaming Systems</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>53165</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Mobile application assisting indoor navigation for people with visual impairments | L’application de téléphone cellulaire assistant la navigation intérieure pour les personnes malvoyantes</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>Mobile application assisting indoor navigation for people with visual impairments | L’application de téléphone cellulaire assistant la navigation intérieure pour les personnes malvoyantes</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>53166</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Anomaly detection in financial transactions using machine learning | Détection des anomalies dans les transactions financières par l’appentissage automatique</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Anomaly detection in financial transactions using machine learning | Détection des anomalies dans les transactions financières par l’appentissage automatique</t>
         </is>
@@ -2207,106 +2239,106 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Keyword Usada</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ID Proyecto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Universidad</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Campus</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Idioma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>51202</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>LLM-Powered Intelligent Educational Systems</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>The deployment of artificial intelligence in online education systems has become very popular in recent years and recently published large language models (LLMs) tend to have a huge application potential on developing intelligent online education systems. This project is to develop and test a personalized online learning system where we will use LLM-powered AI systems like ChatGPT, Gemini, to generate knowledge graphs, personalized learning paths, to plan learning activities, and to conduct adaptive practicing and formative assessment.</t>
         </is>
@@ -2326,290 +2358,290 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Keyword Usada</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ID Proyecto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Universidad</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Campus</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Idioma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>51212</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Soft Wearable Haptic Devices using Magnetic Actuation</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Advances in materials science, chemistry, mechanical engineering, and robotics engineering have brought soft actuators to interactive devices. A wide range of working principles have been used for developing soft actuators: pneumatics, hydraulics, electroactive polymers, acoustofluidics, electrorheological and magnetorheological fluids. However, current soft actuators possess several limitations which include: slow response, low/no force output, difficulty in precisely controlling them, or require high operating voltages with bulky control setups. Pneumatic actuators are commonly used in soft robotics because of their ability to generate large forces but they need high pressure, have low efficiency, are slow in response, and need noisy actuation valves. On the other hand, electrostatic actuators (e.g. dielectric elastomers) provide a high-frequency response but require thousands of volts with bulky control setups. This prohibits the use of these actuation principles in soft wearable settings. Recently electromagnetic actuation has been receiving a lot of attention because of its fast response, lower actuation voltage, and highly programmable and well-controlled movements. However, their deployment in interactive applications is not fully explored. Current state-of-the-art soft magnetic actuators in HCI are limited to low-resolution and enable only subtle vibration feedback. This project aims to develop high-resolution soft magnetic actuators that can deliver high force output and a variety of haptic sensations. By studying, simulating, and investigating novel device architectures, we aim to develop soft actuators that can be precisely controlled and programmed to open up new possibilities in AR/VR, Accessible computing, sports, and rehabilitation.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>51330</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Behavioural Biometrics and the Hidden Risks of User Privacy Violations in Everyday Computing</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Behavioural Biometrics and the Hidden Risks of User Privacy Violations in Everyday Computing</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>51940</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Artificial Intelligence for Sustainable Environment: Towards More Resilient Urban Forests</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Université du Québec à Montréal</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>MONTREAL, Québec</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Artificial Intelligence for Sustainable Environment: Towards More Resilient Urban Forests</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>51158</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Secure LLM-Based Code Generation</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Concordia University</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>51306</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>High-performance practical blockchain systems</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>This is a multi-faceted project on improving core blockchain components in order to improve its performance. Students will be in charge of investigating one or more aspects of blockchains, formulating novel problems, designing, implementing, and evaluating their solution. The objectives of this project include the following. Note that students are expected to choose a subset of goals to fulfill: 1- Investigate relevant blockchain use cases in the public and private sectors, identify suitable blockchain platforms, and develop Proof-of-Concept applications. This includes: cryptocurrencies, NFTs, supply chain traceability, etc. 2- Develop and improve upon existing consensus algorithms, such as Proof-of-Work, PBFT, to support more peers, provide a higher transaction throughput, and deliver predictable commit times. 3- Improve the blockchain data structure (e.g., Merkle tree) for fast insertion, querying, and compressibility. Propose new blockchain structures (e.g., tree) with increased transaction parallelism. 4- Propose a data structure for storing off-chain information, with on-chain verification mechanisms, and a dynamic algorithm for offloading data. 5- Study the effect of networking on blockchain commit time, resilience to attacks, and fork rate. Develop networking protocols for enhanced performance. 6- Create blockchain middleware, delivering reusable services in a reliable and safe manner, such as messaging, identity management, replication, etc. 7- Integrate quantum technology to improve the security of blockchains, such as QRNG (quantum random number generation)</t>
         </is>
@@ -2629,153 +2661,153 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Keyword Usada</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ID Proyecto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Universidad</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Campus</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Idioma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>51315</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Development of ReLiS a tool for conducting systematic reviews</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Université de Montréal</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>When a researcher wants to solve a particular problem, he first looks into the scientific literature (published papers) to see what exists on that subject. ReLiS is a tool that helps reduce the number of articles to analyze considerably (typically hundreds to thousands, depending on the topic of the study). ReLiS allows the user to define a systematic process to follow and to automate as many tasks as possible to researchers. When performing a systematic literature review, the researcher extracts information from each paper he reads so that he can observe trends on the subject and better characterize what has already been solved, and identify the next challenge. ReLiS is a generic framework for configuring, installing, and conducting systematic review projects. It offers statistical results on the data collected and on the process itself. ReLiS counts over 100 users world-wide, coming from a diversity of disciplines. It is open-source and available on GitHub. Our users continuously suggest improvements. There are many development projects available for improving ReLiS. These include, but are not restricted to: improving the user interface for large and small screens, adding technical features of a systematic review, automatically publishing the results of the review, automatically generating the documentation of the protocol followed.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>51796</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Interactive Visualization and Debugging of Software Engineering Agents</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Concordia University</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Large language models (LLMs) are now widely used across a broad range of domains and applications. More recently, advances in reasoning capabilities have enabled LLMs to operate as autonomous agents that tackle real-world tasks, such as resolving software repository issues and navigating graphical user interfaces through iterative planning, tool use, and dynamic runtime feedback. Despite this progress, LLM agents still struggle with complex long-context problems involving extended reasoning chains and multi-step interactions. In such cases, it becomes critical to identify which agent (who) made the mistake and at which step (when) the error was introduced. However, existing debugging workflows remain largely manual and lack effective interactive visualization and diagnostic tools for analyzing agent trajectories. This makes it difficult for developers to trace error propagation, inspect intermediate decisions, and understand how failures emerge over the course of long-horizon execution. In this project, we aim to design and implement an interactive system to support the visualization and debugging of AI agents.</t>
         </is>
@@ -2795,983 +2827,983 @@
   <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Keyword Usada</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ID Proyecto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Universidad</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Campus</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Idioma</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>53126</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Designing High-Performance Database Engines for Emerging Hybrid Workloads</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Designing High-Performance Database Engines for Emerging Hybrid Workloads</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>53669</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Investigate Teleportation Technique for Enhance Navigation in Complex Virtual and Augmented Reality Environment</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Investigate Teleportation Technique for Enhance Navigation in Complex Virtual and Augmented Reality Environment</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>53677</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>From Ant to Giant: Comprehensible Teleportation Across Multiple Scales in Virtual Reality</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>From Ant to Giant: Comprehensible Teleportation Across Multiple Scales in Virtual Reality</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>53787</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>User Interfaces for Software Tool Sharing and Discovery among Natural Scientists</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>User Interfaces for Software Tool Sharing and Discovery among Natural Scientists</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>53791</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Large-scale Livestreamed Audience Participation Games</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Audience participation games (APGs) are games that allow spectators watching the game to participate in a way that also gives them an amount of meaningful impact on the game. There is recent interest in understanding how APGs can be designed specifically for livestreamed environments such as Twitch or Discord, as a break between normal stream content or to improve audience engagement. This project will explore potential interaction techniques and game mechanics for livestreamed APGs that enable a large number (100+) of spectators to participate in the game. We have an existing testbed environment developed in Unity that allows comparison of various game mechanics. The testbed is based on a style of game in which players work together to defeat a non-player boss character. This project will expand the testbed to support new game mechanics and and evaluate them with human participants.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>53890</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Evaluating Speech-Based Simulation Training for Aviation Communication</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Air Traffic Control (ATC) communication is a critical skill for aviation students and pilots. Students must listen accurately, use standardized phraseology, respond quickly, and follow correct communication protocols. However, opportunities for repeated low-stakes practice outside instructor-led role-play, simulator sessions, or aircraft time are limited. This project contributes to the development and evaluation of a free and open-source mobile application for aviation communication training. The ATC app presents realistic scenario-based exercises in which students listen to ATC instructions, respond verbally, and receive feedback on their performance. The first scenarios are based on Springbank Airport, which is used by Mount Royal University aviation students. Initial scenario types focus on taxi communication and runway-incursion prevention, since these are safety-relevant areas where communication errors can have serious consequences. The long-term goal is to support additional airports, flight schools, instructor dashboards, student progress tracking, scenario-authoring tools, and pilots seeking refresher practice. By summer 2027, the app is expected to have an initial working prototype and preliminary data collection. The Globalink student will help prepare the project for broader evaluation and future data collections. Possible tasks include processing exported student performance data, improving data structures for multi-turn scenarios, building dashboards to visualize learning trends, preparing anonymized research datasets, improving documentation, testing app workflows, and creating tools that help instructors or researchers interpret student performance. The project is interdisciplinary, involving computer science, aviation faculty, education researchers, statistics collaborators, and undergraduate research assistants. It is suitable for a student interested in software development, human-computer interaction, data analysis, learning analytics, or educational technology. The expected outputs include improved research infrastructure, data visualization tools, documentation, and contributions to an open-source aviation training platform.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>54340</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Full-Stack Deployment of a Web-Based Educational Game</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>We have developed a "Transition to Post-Secondary" game is aimed to prepare high school students with ADHD and Learning Disabilities with the knowledge to transition into university education. This web-based game consists of role playing and life simulation mechanics; learning elements regarding the university lifestyle are contained within the interactive segments of the game. The game features a narrative structure where the player makes friends with both staff and students to simulate an accurate university experience. The task for the Mitacs intern is to perform full-stack deployment of the game, setting up the game with a web-based log in system, front-end, and back-end database so that the game can be used by students from anywhere.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>54404</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>An open-source system for measuring chamber pressure in shooting sports</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>An open-source system for measuring chamber pressure in shooting sports</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>54461</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Towards Unified Explainable Machine Learning Models for Medical Image Analysis</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Towards Unified Explainable Machine Learning Models for Medical Image Analysis</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>54463</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Resolution-agnostic Machine Learning Approaches for Medical Image Analysis</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Resolution-agnostic Machine Learning Approaches for Medical Image Analysis</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>53328</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>PSGA: Compiler-Guided Retrieval-Augmented Generation for Correct and Scalable Parallelization of Scientific Computing Applications</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Concordia University of Edmonton</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>PSGA: Compiler-Guided Retrieval-Augmented Generation for Correct and Scalable Parallelization of Scientific Computing Applications</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>53339</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Mobile Accessible Seamless Agent (MASA) Android App</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>53349</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Virtual Informal Personal (VIP) Chatbot Android App</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>53354</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>VIP Translator Android App</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I15" s="1" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>53364</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>VERAM: Verification-Oriented Evaluation of Retrieval-Augmented Methods for Trustworthy Scientific Code Generation</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Concordia University of Edmonton</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>VERAM: Verification-Oriented Evaluation of Retrieval-Augmented Methods for Trustworthy Scientific Code Generation</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>53372</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Memorize book reading Android App based on GAIOLA</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>53419</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>mFieldtrip application development with RAG-Chatbot</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H18" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>This project aims to upgrade an open mobile application used for a self-guided field course in physical geography. The field course involves real excursions across Alberta, where students are guided by a mobile application in the absence of direct instructor supervision. The app supports learning by drawing students’ attention to key geographical features and providing associated instructional content and field-based activities. The project will require the student to use a cross-platform development environment, such as Flutter, to develop and enhance the mFieldtrip mobile application (iOS/Android). Advanced features will be implemented using up-to-date technologies, including data analytics, optical character recognition (OCR), and field-based tools to support data collection and analysis. In addition, the project will focus on finalizing the mobile application by enhancing usability and refining the user interface design to improve accessibility, intuitiveness, and overall user experience, ensuring the app is both easy and pleasant to use in real field conditions.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>53467</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Generative AI supported Visualized Information Personal (VIP) Reading/Reader Android App</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H19" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Generative AI supported Visualized Information Personal (VIP) Reading/Reader Android App</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>53471</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Driving and Walking Navigation Android App built on Open Street Map and Next-Stop Recommender</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>Driving and Walking Navigation Android App built on Open Street Map and Next-Stop Recommender</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>53472</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Generative AI supported Next Stop Recommender Android App</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>The project is enhancing the following existing research VIP Research Group (https://www.youtube.com/@vipresearchgroup) has: - Next Stop Recommender (https://nextstop.vipresearch.ca/) which can provide users recommendation for their next visit according to the similarity of their behaviours between each others and the connections amongst locations. - he Generative AI (GenAI) supported Note Takers App (https://notetakers.vipresearch.ca) is an innovative tool designed to help users capture and organize notes from spoken conversations, incorporates Public Key Infrasture (PKI), Secure Sockets Layer (SSL) and salted secured hash algorithm. The research project involves three parts: (1) The production server needs to (a) have Open Street Map Tile Server and Routing Server for selected countries and regions; (b) offers endpoints that allows client apps (including the Android App) to download selected region's map; (c) receive the requests for synchronizing users their historical records, preferences and app's configuration anonymously in a secure and privacy protected way; (d) allow administrators to test new Text-Generation, Speech-to-Text, and Text-to-Speech (TTS) GGUF models and auto update available model list and corresponding voice options (for TTS models); (e) offers endpont for accessing server-side services on Text-Generation and Speech-to-Text. (2) The Android App allows users to (a) download an available Text-Generation, Speech-to-Text, and Text-to-Speech (TTS) GGUF model from the production server according to the available model list provided by the endpoint; (b) choose pre-downloaded models and a supported voice from the selected TTS model; (c) ask the app to recommend places to visit for next via talking to the app with natural language; (d) listen to the app to explain the recommendations; (e) use the endpoint the production server offers to synchronize device uuid, corresponding configurations, and historical records anonymously in a secure and privacy protected way. The app can take NoteTakers' secure communication workflow and design as reference (see https://maiga.athabascau.ca/#notetakers and https://notetakers.vipresearch.ca).</t>
         </is>
@@ -3783,42 +3815,42 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>53534</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Understanding LLM Reasoning Unfaithfulness</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Large language models often produce step-by-step "reasoning" before giving an answer, and users increasingly trust these explanations. But a model's stated reasoning may not reflect what actually drove its answer. It can rationalize after the fact, hide the cues it truly relied on, or be steered by signals it never mentions. This gap, known as reasoning unfaithfulness, is a serious problem for safety, trust, and oversight of modern AI. This project investigates when and why LLM reasoning becomes unfaithful. The student will design controlled experiments that probe whether a model's chain-of-thought genuinely explains its behavior, measure faithfulness across tasks and model families, and explore how factors like post-training and adversarial manipulation affect it. The work combines hands-on experimentation with open-source models, careful evaluation design, and analysis of results. The intern will gain experience in trustworthy machine learning, LLM evaluation, and research methodology and contribute to findings suitable for a workshop or conference submission.</t>
         </is>
@@ -3830,42 +3862,42 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>53734</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Efficient Training of Diffusion Models</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Carleton University</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>This project aims to develop novel optimization objectives that accelerate the training and inference of diffusion models. While modern diffusion models can achieve high-fidelity data generation, their reliance on lengthy denoising chains imposes prohibitive computational costs. Recent developments on temporal consistency show promising results without incurring a high computational cost. By designing alternative loss functions that leverage geometric shortcuts, this research seeks to reduce the number of training and inference steps for diffusion models. This project aims to develop general objectives for various diffusion architectures, making them more computationally viable for resource-constrained applications.</t>
         </is>
@@ -3877,42 +3909,42 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>53930</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Feature Selection for High Dimensional imbalanced Problems</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Feature selection methods are essential to deal with high dimensional tasks. In this project, we will tackle the problem related with high dimensional imbalanced problems. To address this problem, we will implement and test standard feature selection methods, and novel feature selection methods developed for high dimensional imbalanced problems. The main goal is to develop a novel feature selection method that is suitable for high dimensional problems that also suffer from class imbalance. The key idea is to take into account the relation between the features and the classes, especially the minority one in order to prevent a performance degradation in this class.</t>
         </is>
@@ -3924,42 +3956,42 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>53931</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Multi-Task Active Learning</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>In many real-world predictive problems, the available data has frequently a vast majority of instance unlabelled while only a small number of instances is labelled. This happens because the labeling process is often both expensive and difficult, requiring an expert or a team of experts to do the job. Active learning is a strategy that allows us to select the most useful cases to be labelled by experts. Ideally, the selected cases should be the ones that will benefit the more the learning algorithm that is being used. Another important aspect of these data sets is the fact that in some situations the same data can be used for multiple prediction problems, i.e., the same data set can be used to obtain the predictions for several tasks. For instance, a data set with movies reviews, can be used to predict the movie genre, the number of stars it will reach or the profit it will generate. In this project our main goal is to address the multi-task problem in a semi-supervised context through the application of active learning. We will start by implementing and testing basic active learning independent methods for each predictive task. A consensus will be derived to decide for which cases a label will be obtained. Then, we will proceed with the implementation of experiments for comparing the performance of: i) this baseline strategy; alternative ways for obtaining the consensus through weights; and the combination of basic selection strategies with outlier detection and resampling methods. This project main outcomes are: - the development of novel solutions for the multi-task active learning problem; - the experimental comparison of of several alternative solutions; - a report in the form of a research paper describing the algorithms proposed and main results.</t>
         </is>
@@ -3971,42 +4003,42 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>53935</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Deep Learning for Imbalanced Data</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Deep learning has gained a vast popularity. These methods are nowadays applied across different applications and domains. Still, the relation between the use of deep learning methods in imbalanced problems is under-explored. The main goal of this project is to investigate this relation, with a special focus on the complexity of the trained models. We will set up experiments to observe the impact of applying deep learning models under problems with different imbalance ratios and different task complexities (class overlap, small disjunct, high dimensionality, etc...). We will aim at understanding the impact of the imbalance and other characteristics in the performance of these models considering different model architectures and complexity.</t>
         </is>
@@ -4018,42 +4050,42 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>54076</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Decision-focused Learning for Distributed Energy Resource Optimization</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Modern power systems are facing increasing uncertainty from both the supply side, due to the integration of renewable energy, and the demand side, due to emerging large energy consumers such as AI-focused data centers. These uncertainties complicate the control and optimization of energy resources, where system operators need to predict uncertain quantities and then make operational decisions based on the predicted parameters. A commonly adopted approach treats prediction and optimization as two separate stages: first, a machine learning model is trained to predict unknown parameters from observed features; then, an optimization problem is solved using the predicted parameters. However, machine learning predictions are rarely perfect, and prediction errors can propagate to the downstream optimization problem, leading to suboptimal or risky decisions. To address this challenge, this project explores decision-focused learning, an end-to-end paradigm that learns predictive models in a way that is directly informed by the loss of the downstream optimization task. We will study decision-focused learning for the optimization of distributed energy resources (DERs), such as battery storage and electric vehicles. We will start with a storage arbitrage problem, where a grid-scale energy storage operator predicts electricity prices and determines charge/discharge decisions to maximize profit while accounting for prediction errors and financial risk. We will first apply standard decision-focused learning to this problem and compare its performance with the conventional two-stage approach that considers prediction and optimization separately. Next, we will incorporate uncertainty quantification into decision-focused learning by leveraging calibrated uncertainty estimates in a downstream robust optimization problem, with the goal of further controlling risk in storage arbitrage. Building on these approaches, we will further study DER management problems that involve uncertain renewable generation and uncertain consumer demand. The goal is to reduce operational costs of DERs while explicitly accounting for uncertainty and risk.</t>
         </is>
@@ -4065,42 +4097,42 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>54161</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Energy Storage-Assisted Scheduling under Grid Capacity Constraints</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>The rapid growth of large energy consumers, such as AI data centers and electric vehicle charging fleets, is creating new operational challenges for power grids. These loads can be large, time-varying, and highly concentrated, while grid capacity expansion is often slow, costly, and constrained by planning and permitting processes. As a result, limited grid capacity may become a major barrier to the timely deployment of large energy-consuming infrastructures. This project studies how energy storage can be co-optimized with large energy consumers to reduce grid capacity requirements and lower electricity costs. The key idea is to use storage as a flexible resource: it can be charged during periods of low system demand or low electricity prices, and discharged during peak-demand periods. In this way, storage can smooth the net load seen by the grid, reduce peak power draw, and improve the economic operation of the system. We will first formulate the optimal scheduling problem for energy storage under given grid capacity, demand profiles, storage constraints, and electricity prices. This offline optimization model will provide a benchmark for evaluating system performance and understanding the value of storage. Building on this formulation, we will develop real-time scheduling methods, including model predictive control, to handle uncertain and time-varying demand and prices. The proposed methods will be evaluated using real-world data traces. The goal is to develop practical optimization tools for storage scheduling and capacity planning that support the cost-effective and scalable deployment of large energy-consuming infrastructures under grid capacity constraints.</t>
         </is>
@@ -4112,508 +4144,508 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>54217</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Conversational AI for Older Adults</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Carleton University</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>Older adults face increasing barriers to digital participation. Conversational agents powered by artificial intelligence (AI), such as ChatGPT, Google Gemini, and Microsoft Copilot, are transforming the way people gather information, learn, and support their well-being. However, these systems are rarely designed to be inclusive of the needs of older adults (people 60+ years old), especially for their on-the-go, context-aware use. This research addresses these issues through the development of conversational AI agents that integrate contextual information with large language models to provide on-the-go, just-in-time assistance for older adults. These systems can be life changing and enable a new level of independence for older adults, especially those with disabilities such as mild cognitive impairment, mobility issues, or vision loss, at a more accessible price point when compared to existing smart home alternatives (e.g., through purchasing one system instead of multiple peripherals that must be installed around a smart home). This research sits at the intersection of user experience design, digital inclusion, aging, and technology. Aspects core to the project include inclusive design, accessibility, iterative design, and design thinking. The application will first start as a preliminary prototype and refined through several iterations into a developed application. The created application will be evaluated with stakeholders, including older adults, their caregivers, and members of the project team. Evaluation criteria will include but not limited to: usability, accessibility, inclusiveness, acceptability, and user perceptions. No prior work has explored integrating wearable computer vision systems into conversational AIs for inclusive aging support. Thus, conversational agents embedded in wearables (e.g., smart glasses) will be the primary focus of this project, but this may change depending on evolving needs of the project and users.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>51231</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Expressive Interaction with AI</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Université de Montréal</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Interacting with an AI, such as a large language model (LLM), is typically done through textual prompts in a chat-like interface. While easy to use, this interaction is often slow and ambiguous. This is particularly true when AI is used to help with creative tasks such as drawing or writing. In this project, we aim to explore alternative ways of interacting with AI. Examples include the use of digital instruments, gestural interaction, or even sketching. Specifically, the idea would be to understand the needs of creative professionals (e.g., artists, writers, and even programmers) and to develop tools to support their work. Feel free to check out examples of such interactions developed in my research group: https://damienmasson.com/pdfs/directgpt.pdf and https://damienmasson.com/pdfs/textoshop.pdf.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>53509</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Code in artist's social media</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Université de Montréal</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>Generative artists write code, run code, tweak code in order to generate artworks. Many artists share the artworks on online platforms, such as instagram or bandcamp. Sometimes, artists also share the code. Sharing code can have mutliple meanings: cool medium, transparency, generosity, traceability. Sharing code can take several forms, such as posting a link to a code repository along a social media post, sharing a picture or screencast of the code that performs the artworks, or it might be that the act of writing code is part of the artistic performance. In this project, the student will develop novel methods to collect source code that is shared on social media platforms. The goal is to explore these different practices of artistic code sharing as well as the different motivations of artists for sharing code. https://spectrum.library.concordia.ca/id/eprint/992759/1/Thow_MA_F2023.pdf https://www.google.com/search?q=%22github.com%22+site%3Abandcamp.com https://youtu.be/ca7xzqR7WaY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>53511</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Full stack software specialization</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Université de Montréal</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Software applications depend on a large number of dependencies: third-party libraries that provide reusable features, language standard libraries, containers that provide reproducible environments for release and distribution. This vast network of dependencies forms the software supply chain of the application. This software supply chain provides all the benefits of software reuse: share development of generic features, reduction of development time. Yet, it also introduces challenges regarding reliability, security and performance. A key part of these challenges comes from the fact that all reused components are generic so they can be reused in many different contexts, but a specific application uses only a fraction of each reused component. In this internship, the student will investigate opportunities to specialize the software supply chain of an application at different levels of the stack (libraries, standard library and container). This will involve static and dynamic code analysis to determine which parts of the software supply chain are used, as well as code transformation to specialize the supply chain. https://arxiv.org/pdf/2302.08370 https://dl.acm.org/doi/pdf/10.1145/3274694.3274703 https://www.usenix.org/system/files/raid20-ghavamnia.pdf</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>53517</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Niche code sharing platforms</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Université de Montréal</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>The vast majority of public source code is hosted on Github. Yet, there exists many alternative to host and share source code, such as codeberg, Gitea, sourcehut, or forgejo. These alternatives are niche and mostly used by contributors who explicitly seek alternatives to Github. These motivations can be autonomy, independence, subversion, cultural artistic. In this internship, we study the open source communities who turn to these alternative, niche, code hosting platforms. We mix code analysis, text analysis and interviews, to categorize the types of projects that are hosted on these platforms, as well as the motivations of the contributors and communities. https://dl.acm.org/doi/pdf/10.1145/2702123.2702549 https://fupress.org/journal/JSCADD/index.php/journal/article/download/63/27 https://www.reddit.com/r/foss/comments/1mpf69k/codeberg_sourcehut_or_other/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>53546</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Building Trustworthy Digital Twins with LLMs and Formal Methods</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>École Polytechnique de Montréal</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>53948</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Multimodal Large Language Models for document understanding</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>This project aims to develop multimodal large language models (MLLMs) capable of understanding, interpreting, and reasoning over complex documents that combine text, images, tables, charts, and diagrams. Rather than training foundation models from scratch—which would require prohibitive amounts of data and computational resources—the project will focus on efficiently adapting and fine-tuning existing state-of-the-art MLLMs for document understanding tasks. Particular emphasis will be placed on parameter-efficient adaptation methods, reducing annotation requirements through self-supervised and weakly supervised learning, and improving model efficiency. Applications include scientific literature analysis, technical documentation, administrative and legal document processing, and intelligent information retrieval systems.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>53958</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Emotion Recognition with Multimodal Large Language Models</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>This project aims to develop methods for recognizing human emotions using multimodal large language models (MLLMs) that can jointly process and reason over multiple sources of information such as facial expressions, speech, text, and contextual signals. The goal is to move beyond single-modality emotion recognition by leveraging the complementary nature of different modalities to obtain more robust and accurate predictions. Rather than training models from scratch, the project will focus on adapting and fine-tuning existing multimodal foundation models to emotion understanding tasks, making use of parameter-efficient learning strategies and limited labeled data. A key challenge is to effectively align and fuse heterogeneous signals (e.g., visual cues from facial expressions, acoustic features from voice, and semantic information from language) into a coherent representation of emotional state. The resulting models are expected to improve performance in real-world, noisy, and unconstrained environments, with applications in human-computer interaction, affective computing, mental health monitoring, and user behavior analysis.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>53960</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Efficient Autoregressive Generative Modelling</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>This project focuses on improving autoregressive generative models for image synthesis, with a particular emphasis on how images are represented and encoded into discrete tokens. Autoregressive models generate images token by token, but their effectiveness strongly depends on the quality and efficiency of the underlying tokenization process. The main goal of this project is to design more efficient and informative visual token representations that reduce redundancy while preserving semantic and structural content. This includes investigating improved image token encoders, more compact discrete representations, and alternative ways of organizing visual information for autoregressive modeling. A key objective is to reduce computational cost and sequence length during both training and inference, while maintaining or improving image generation quality. The project will explore methods such as learned visual tokenizers, compression-aware representations, and structure-preserving encoding schemes. The resulting methods aim to make autoregressive image generation more efficient and scalable, enabling higher-quality synthesis with reduced computational resources.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>53991</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Verified Concurrent Algorithms</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Université du Québec à Montréal</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>The MOST programming language (Kavanagh and Pientka, 2024) extends traditional session-typed languages with concurrent type-level computation to more precisely specify communication protocols. In particular, protocols specifications are very restricted concurrent programs that generate a communication protocol based on past communications in a system. MOST users write both a program and its protocol specification, and MOST's type system ensures that the program respects its specification. This project will use MOST to specify and verify concurrent algorithms and data structures, including stacks, queues, and concurrent hash-tries. Since concurrent algorithms and data structures are often described in terms of shared memory, they will need to be redesigned to be implemented as a collection of interacting processes. We will draw inspiration from the literature and from open-source software projects to produce other case studies. These case studies will inform future development of MOST, form a reusable library of verified concurrent algorithms, and help develop principles for specifying concurrent algorithms and data structures in this setting.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>54048</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>EN: Artificial intelligence methods to automate video surveillance in metro stations \ FR: méthodes d'intelligence artificielle pour automatiser la vidéosurveillance dans les stations de métro</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Université TÉLUQ</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>EN: Artificial intelligence methods to automate video surveillance in metro stations \ FR: méthodes d'intelligence artificielle pour automatiser la vidéosurveillance dans les stations de métro</t>
         </is>

--- a/mitacs_proyectos_ciudades_pastel.xlsx
+++ b/mitacs_proyectos_ciudades_pastel.xlsx
@@ -476,18 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,40 +499,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>ID Proyecto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Universidad</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Campus</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Idioma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
@@ -545,40 +551,45 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
           <t>51360</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Robust Aggregation for Multi-Node LLM Inference</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>As large language models are increasingly deployed in distributed and multi-party settings, ensuring the reliability and integrity of their outputs becomes a critical challenge. In such settings, a single model instance may not be sufficient to guarantee trustworthy responses which could be due to resource constraints, fault tolerance requirements, or the need for redundancy. Distributed LLM inference, where multiple model instances collaborate to produce a final output, offers a promising direction, but introduces new challenges around consistency, coordination, and adversarial robustness. This project investigates robust aggregation mechanisms for distributed LLM inference in the presence of adversarial or unreliable nodes. In a multi-node inference setting, responses from multiple LLM instances must be aggregated into a single reliable output. This process that becomes challenging when some nodes behave maliciously, are compromised, or return inconsistent results, degrading overall system trustworthiness. The goal is to design and evaluate an aggregation layer that improves the reliability and robustness of distributed inference. This involves exploring strategies to detect inconsistent or outlier responses and select or synthesize outputs that reflect consensus across nodes. The work involves understanding how different aggregation approaches perform under varying levels of adversarial pressure, and what trade-offs emerge between robustness, accuracy, and computational overhead. The project will also examine whether aggregation strategies can be made adaptive, adjusting their behavior based on observed node reliability over time. The system will be evaluated under a range of adversarial scenarios, including random incorrect outputs, coordinated malicious responses, and subtle misinformation attacks. Beyond adversarial robustness, the project will also consider practical deployment constraints such as latency and scalability, ensuring that the proposed mechanisms remain viable in real-world distributed settings. Key evaluation metrics will include response accuracy, attack resilience, latency, and system efficiency.</t>
         </is>
@@ -592,40 +603,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t>51375</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Agentic Security Analysis for Detecting and Mitigating Fraudulent Cross-Chain Messaging</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Agentic Security Analysis for Detecting and Mitigating Fraudulent Cross-Chain Messaging</t>
         </is>
@@ -639,40 +655,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>51430</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Monitoring and Analyzing Cross-Layer Messaging in Blockchain Layer 2 Architectures</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Monitoring and Analyzing Cross-Layer Messaging in Blockchain Layer 2 Architectures</t>
         </is>
@@ -686,40 +707,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>52201</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Implementation of Lightweight Semantic Communication Models for Intelligent IoT Systems</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Implementation of Lightweight Semantic Communication Models for Intelligent IoT Systems</t>
         </is>
@@ -733,40 +759,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>52202</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>AI-Assisted Wireless Link Selection for Reliable IoT and V2X Networks</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>This project investigates AI-assisted wireless link selection for reliable IoT and vehicle-to-everything (V2X) networks. In many wireless systems, devices must decide which communication link, relay, access point, or neighbouring node should be used to transmit data. Poor link selection may increase packet loss, delay, and information staleness, especially when devices are mobile or when channel conditions change over time. The student will develop a Python-based simulation framework for a simplified IoT or V2X network. Nodes may represent sensors, vehicles, roadside units, or access points. The simulator will model basic wireless link quality using distance, path loss, noise, interference, or random channel variation. The student will implement and compare several link-selection strategies, including shortest-distance selection, strongest-signal selection, random selection, and simple machine-learning-based prediction. The project will evaluate performance using metrics such as packet success rate, delay, link reliability, number of failed transmissions, and possibly Age of Information. The emphasis is on implementation, experimentation, and visualization rather than advanced wireless theory. The expected outcomes include well-documented simulation code, performance plots, and a short technical report explaining which link-selection strategies work best under different network conditions. This project is suitable for students interested in wireless networks, IoT, vehicular communications, machine learning, simulation, and data analysis.</t>
         </is>
@@ -780,40 +811,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>52203</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Implementation of Trust-Aware Security Mechanisms for IoT and Vehicular Edge Networks</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Implementation of Trust-Aware Security Mechanisms for IoT and Vehicular Edge Networks</t>
         </is>
@@ -827,40 +863,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>52204</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Graph-Based Simulation of Freshness-Aware Resource Allocation in Edge-IoT Networks</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Graph-Based Simulation of Freshness-Aware Resource Allocation in Edge-IoT Networks</t>
         </is>
@@ -874,40 +915,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>52538</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Reliability-Aware Workload Generation for LLM Serving Systems</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -917,40 +963,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>51257</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Visual Motion Analysis from Images and Videos</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>University of Alberta</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>This project focuses on analyzing visual behaviors of articulated objects (human and animals) from video feed, a problem that plays a crucial role in many real-life applications ranging from natural user interface to autonomous driving. As a member of the Vision and Learning Lab at the University of Alberta (https://vision-and-learning-lab-ualberta.github.io/), you are expected to work with a graduate student/Postdoc researcher, get familiar with state-of-the-art deep learning, quantum machine learning and computer vision techniques, and gain hands-on research experience on benchmark and home-grown datasets. There are ample opportunities to be involved in exciting research topics in computer vision and to publish</t>
         </is>
@@ -964,40 +1015,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>51942</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Student engagement detection in online learning</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Online learning plays a key role in today’s education system. Engagement detection in online learning is crucial as the student’s success in online courses heavily depends on his/her state of mind. In this paper, we will use student’s behavioral, emotional, and cognitive dimensions for engagement detection. Different machine learning and deep learning approaches will be used to analyze facial expressions and forum posts in online courses. We will perform empirical studies and develop prototype applications to test and explore theoretical concepts on student engagement detection in online learning platform.</t>
         </is>
@@ -1011,40 +1067,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
           <t>51943</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Visualization of educational data in online learning</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>Educational institutions capture huge amounts of educational data, especially in online learning. Data mining techniques have shown promises to interpret these data using different patterns. However, understanding the mining patterns and extracting meaningful information from the data require reasonable skills and knowledge for the users. Information visualization, due to its potential to display large amount of data, may fill this gap. In this research project, we will analyze various visualization techniques to represent meaningful information from the educational data, especially dealing with monitoring student performance, understanding learning style, analyzing course and program status, and dropout prediction. We will develop a learner- or instructor-focused effective visualization system for online learning environment.</t>
         </is>
@@ -1058,40 +1119,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
           <t>51944</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Early dropout prediction in e-learning courses using machine learning</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>High dropout rate is a major concern for many universities that offer online courses. If the dropout-prone students can be identified at their early stages of learning, the dropout rate can be reduced by providing individualized support to the students at-risk. Due to the electronic nature of the learning management systems (LMS), various attributes of the students’ progress can be monitored and analyzed over time. The main objective of this project is to explore what progress information about a student can be used from LMS and how this information can be used with a classification model to predict the students at risk. Different machine learning and deep learning methods will be investigated for early dropout prediction in this research project.</t>
         </is>
@@ -1105,40 +1171,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
           <t>51945</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Pedagogical Intervention Design for Online Learners</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>Designing pedagogical interventions based on student's engagement detection is a challenging research problem. In this research, we will explore the use of engagement detection and learning analytics to automate personalized pedagogical support for online learners, specifically to answer the following questions: at what point and with what frequency should the students be consulted? why are they being consulted? what intervention should be provided? How will the pedagogical interventions integrate with the rest of the teaching and learning practices? We will investigate this area and develop a demo program on pedagogical intervention for the online learners.</t>
         </is>
@@ -1152,40 +1223,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
           <t>52076</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Applications of Artificial Intelligence and Reinforcement Learning in Assessment of Thyroid Nodule Using Ultrasound</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>University of Alberta</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>Applications of Artificial Intelligence and Reinforcement Learning in Assessment of Thyroid Nodule Using Ultrasound</t>
         </is>
@@ -1199,40 +1275,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
           <t>52255</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Secure Retrieval-Augmented Generation Against Poisoning Attacks</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Concordia University of Edmonton</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Retrieval-Augmented Generation (RAG) systems enhance large language models (LLMs) by integrating external knowledge retrieval into the generation process. While RAG improves factual accuracy and domain adaptability, its dependence on external knowledge sources introduces serious security vulnerabilities, particularly poisoning attacks. In these attacks, adversaries inject malicious or misleading documents into the knowledge base so that the retriever selects poisoned content during inference, causing the LLM to generate manipulated, biased, or harmful responses. Such vulnerabilities pose significant risks for real-world applications in healthcare, finance, education, and cybersecurity. This research project aims to develop a secure and robust RAG framework capable of detecting and mitigating retrieval-layer poisoning attacks. The project will investigate how poisoned documents affect retrieval rankings, embedding representations, and downstream text generation in modern RAG architectures. Various attack strategies, including semantic poisoning, adversarial document injection, stealthy trigger-based attacks, and retrieval manipulation techniques, will be explored to understand their impact on system reliability and trustworthiness. To improve RAG security, the research will examine defense mechanisms such as anomaly detection, secure reranking, retrieval filtering, embedding consistency verification, and trust-aware retrieval strategies. Privacy-preserving techniques and robust retrieval optimization methods will also be investigated to reduce the influence of malicious content while maintaining retrieval quality and generation accuracy. The expected outcome of this research is a scalable and attack-resilient RAG framework that enhances the security, reliability, and trustworthiness of LLM-based systems operating in adversarial environments. The proposed framework will contribute toward the safe deployment of AI-driven knowledge systems in critical real-world applications.</t>
         </is>
@@ -1246,40 +1327,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
           <t>52296</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>A deep normative model of the human brain from MRI data</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>MacEwan University</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>The project involves analysis brain MRI data. In neuroimaging is important to understand how brain structures are changing due to normal ageing or disease. The goal of this project is to generate a model of the ageing human brain and relate disease populations to this model. We will work with medical data provided by our collaboration between the Computing Science Department and the Department of Neurology, at University of Alberta. Preliminary work from our group [1,2] has been done to create a shape model of the healthy hippocampus. The model uses a variational graph convolutional autoencoder conditioned by age. The proposed project extends this model to study full brain atrophy and cortical thickness variability. The focus for next summer is to create a normative model of healthy brain surface from a large collection of MRI images (ex UKBiobank). Disease-related abnormalities will be defined as deviations from this model. For the diseased population we will use internal data (ALS patients) and ADNI data (AD patients). The results of this project will be interpreted by our medical collaborators and summarized in a publication. [1] Kiechle J., Miller D., Slessor J., Pietrosanu M., Beaulieu C., Cobzas D. (2023). Explaining anatomical shape variability International Symposium on Biomedical Imaging 2023 [2] Rabbi J., Kiechle J., Beaulieu C., Ray N., Cobzas D. (2024) Disentangling Hippocampal Shape Variations, MELBA journal, November 2024</t>
         </is>
@@ -1293,40 +1379,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
           <t>52390</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Agentic Federated Learning for Adaptive IoT Intrusion Detection</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Concordia University of Edmonton</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Agentic Federated Learning for Adaptive IoT Intrusion Detection proposes an intelligent and privacy-preserving cybersecurity framework for detecting malicious activities in heterogeneous Internet of Things (IoT) environments. The project integrates Federated Learning (FL) with autonomous AI agents to enable adaptive, scalable, and communication-efficient intrusion detection across distributed IoT devices without requiring the sharing of raw data. Inspired by recent advances in Agentic Federated Learning, the framework leverages specialized collaborative agents to automate the design, optimization, and deployment of FL-based intrusion detection strategies. Traditional FL-based intrusion detection systems often rely on static configurations and predefined aggregation mechanisms, making them vulnerable to evolving cyberattacks, device heterogeneity, non-IID traffic distributions, and communication constraints commonly observed in IoT ecosystems. To address these limitations, the proposed framework introduces multiple intelligent agents responsible for planning, optimization, threat analysis, communication management, and adaptive response generation. These agents continuously monitor network conditions and dynamically adjust federated training strategies, client participation, and defense mechanisms to improve detection performance and system robustness. The proposed architecture follows a multi-stage workflow consisting of planning, programming, optimization, and deployment phases, similar to the human software engineering lifecycle. A planning agent identifies suitable FL configurations and security requirements, while coding and optimization agents iteratively refine intrusion detection models using simulated IoT attack scenarios. Deployment agents further adapt the optimized framework for practical FL platforms such as Flower or FedML. The research aims to develop an adaptive and autonomous intrusion detection framework capable of mitigating sophisticated cyber threats such as distributed denial-of-service (DDoS), botnet attacks, and poisoning attacks in decentralized IoT networks. The proposed system is expected to improve detection accuracy, communication efficiency, privacy preservation, and resilience against adversarial behaviors in real-world IoT deployments.</t>
         </is>
@@ -1340,40 +1431,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
           <t>52391</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Agentic Multimodal Fake News Detection</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Concordia University of Edmonton</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Agentic Multimodal Fake News Detection proposes an intelligent framework for identifying and mitigating misinformation by integrating multimodal learning with autonomous AI agents. The project aims to detect fake news by jointly analyzing multiple information sources, including textual content, images, audio, video, social context, and metadata, while enabling adaptive reasoning and evidence verification through collaborative agent-based decision-making. Traditional fake news detection systems primarily rely on static classification models that process textual or visual information independently. However, modern misinformation campaigns frequently combine manipulated images, misleading captions, synthetic audio, AI-generated videos, fabricated social interactions, and coordinated dissemination strategies, making single-modal and fixed detection approaches insufficient. Furthermore, existing systems often lack reasoning capability, explainability, and the ability to dynamically verify information using external knowledge sources. Inspired by recent advances in agentic AI systems and multi-agent collaboration, the proposed framework introduces specialized autonomous agents responsible for different analytical tasks. A text analysis agent examines linguistic patterns, semantic inconsistencies, and misleading narratives, while visual analysis agents identify manipulated or out-of-context images and videos. Additional agents analyze synthetic or manipulated audio, social propagation behavior, user interaction patterns, and metadata anomalies to assess the credibility and origin of content. Evidence retrieval and fact-verification agents further leverage Retrieval-Augmented Generation (RAG), large language models (LLMs), and multimodal transformers to validate claims using trusted external knowledge sources. These agents collaboratively interact through an adaptive workflow that continuously refines detection decisions based on contextual and multimodal evidence, improving explainability, robustness, and adaptability against emerging misinformation strategies, including AI-generated fake media and coordinated disinformation campaigns. This research contributes toward the development of trustworthy and intelligent misinformation detection systems capable of supporting digital media platforms, public information services, and online social networks in combating the rapid spread of fake news.</t>
         </is>
@@ -1387,40 +1483,45 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
           <t>52868</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>EN: Toward Sustainable AI - Assessing and Reducing the Environmental Footprint of AI Models // FR: Vers une IA durable - Évaluation et réduction de l’empreinte environnementale des modèles d’IA</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Royal Military College of Canada</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Kingston</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Kingston, Ontario</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>EN: Toward Sustainable AI - Assessing and Reducing the Environmental Footprint of AI Models // FR: Vers une IA durable - Évaluation et réduction de l’empreinte environnementale des modèles d’IA</t>
         </is>
@@ -1434,40 +1535,45 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
           <t>51768</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Deep learning for integrating multimodal data for precision medicine</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Western University</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>London, Ontario</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Omics data refers to the high-dimensional and highly correlated data from genomics, transcriptomics, microbiome, metabolomics, and proteomics. Different computational and statistical analyses of these data can be used to identify risk factors for different diseases or to build autonomous disease prediction models. Analysis of omics data, imaging, and medical health records has become very popular in disease studies because such analysis is helpful to predict whether a patient has a certain disease or not. It is expected that integration of knowledge from multiple data sources measured on the same individuals should improve the prediction performance of patients with chronic diseases. Because one of these data sources may have biological knowledge that is absent in another one. However, due to the high-dimensional nature of the data sets with hundreds of thousands of variables and very small numbers of samples, traditional machine learning approaches (e.g. Support Vector Machines) have limitations to analyze these data efficiently. To overcome these limitations, the project will apply deep learning algorithms to learn knowledge from multiple data sources (omics, imaging, medical health records, etc.) at different feature levels, which will be used to predict disease outcomes and potential drug targets for the diseases. Specifically, the project will have these two objectives: 1) Apply deep learning algorithms to learn knowledge across data sources at a single feature level. 2) Apply transfer learning algorithms to learn knowledge across feature levels. Key Words: bioinformatics, computational biology, computer science, statistics, computing engineering, artificial intelligence, biostatistics, genome science, machine learning, algorithms, mathematics</t>
         </is>
@@ -1481,40 +1587,45 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
           <t>51769</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Quantum equivariant diffusion model for 3D de novo molecule design</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Western University</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>London, Ontario</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Introduction Although state-of-the-art models such as equivariant diffusion models have achieved significant progress in generating realistic molecular structures, they still encounter limitations in handling the high-dimensional complexity and ensuring time efficiency. We hypothesize that quantum machine learning can potentially solve these problems. Therefore, we propose a Quantum Equivariant Diffusion Model (QEDM) for 3D de novo molecule design, which aims to enhance the quality of generated molecules while reducing both training and inference times. This innovative approach leverages the unique capabilities of quantum computing to overcome the inherent limitations of classical methods, promising substantial improvements in the efficiency and accuracy of molecular design. Research goal The overarching goal of this study is to build a QEDM to generate 3D de novo molecules with desired properties. Proposed analysis We will build our QEDM on the quantum platform (https://quantum.ibm.com/) provided by International Business Machines corporation (IBM). The QEDM will leverage a two-step process: a forward diffusion process and a backward denoising process. In the forward process, we will employ a non-unitary depolarizing channel to progressively add noise to the quantum-encoded representation of a molecular structure, transforming it into a maximally mixed state. Each molecule is initially represented by its atomic coordinates and types, which will be encoded into quantum states using amplitude encoding. The noise schedule will be designed using a cosine function to ensure a gradual and controlled transformation. For the backward process, we will implement a parameter-sharing quantum circuit that denoises the quantum states. This circuit will include a timestep embedding circuit to incorporate temporal information and a denoising circuit that processes the noisy quantum state along with the timestep embedding state. The quantum circuits will be designed with gates that implement rotations and translations consistent with the physical symmetries of the molecule, ensuring equivariance. Key Words: Physics, computational biology, computer</t>
         </is>
@@ -1528,40 +1639,45 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
           <t>53116</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Text-Image Generalization Unlearnable Examples</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Western University</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>London, Ontario</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>While unlearnable examples have been actively studied for classification-oriented data protection, how to design effective unlearnable examples for text-image generative models remains underexplored. In this project, we will address several fundamental aspects of unlearnable visual protection for diffusion-based image editing. Ideally, the project will end up with a paper published at a top-tier ML/CV conference, such as CVPR, ICML, or NeurIPS. The key strengths/objectives of our project include: -- We will leverage the tools from representation learning and optimization principles to develop new theoretical and algorithmic insights for text-image generalization unlearnable examples. In other words, we will study how protected images can disrupt the correspondence between visual semantics and text-guided editing instructions, thereby motivating a principled protection framework for diffusion-based image editing. -- Our proposed framework will also support robustness against diverse editing requests, which are common in real-world text-image applications. For diffusion-based image editing, there exist several challenging scenarios: 1) instruction-dependent editing, where different text prompts may require modifying different semantic attributes, such as object appearance, background, style, or local structure; 2) model-dependent generation, where different diffusion models may rely on different visual-text representations and editing mechanisms. We will design principled methods to address these issues, so that protected images remain visually natural to humans but become difficult for diffusion models to correctly edit or exploit under diverse text-guided editing conditions.</t>
         </is>
@@ -1575,40 +1691,45 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
           <t>53117</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Trustworthy AI for Data Privacy: Protecting Personal Data in the Era of Pretraining</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Western University</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>London, Ontario</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Trustworthy AI for Data Privacy: Protecting Personal Data in the Era of Pretraining</t>
         </is>
@@ -1622,40 +1743,45 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
           <t>53118</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Foundation Prior-data Fitted Network Models for Scientific Discovery</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Western University</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>London, Ontario</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>This project aims to develop efficient foundation models for scientific discovery, with a focus on prior-data fitted networks (PFNs), in-context learning, and transfer learning. Many scientific problems in biology and biomedicine involve limited labeled data, heterogeneous measurements, expensive experiments, and distribution shifts across labs, patients, platforms, and experimental conditions. Standard deep learning methods often require task-specific training, extensive tuning, and large datasets, making them difficult to use in these data-limited scientific settings. PFN-style models offer a promising alternative: by learning from broad families of prior-generated tasks, they can make fast predictions on new datasets directly from context, without costly retraining. The project will pursue three connected objectives: -- We will design scientific priors and task-generation processes that capture useful structures in biological and biomedical data, such as tabular clinical variables, molecular features, perturbation responses, single-cell measurements, and multimodal embeddings. These priors will help encode realistic assumptions about noise, sparsity, causal structure, and cross-experiment variation. -- We will build efficient foundation model architectures that can transfer knowledge across datasets, tasks, and modalities while remaining computationally practical. This includes studying long-context prediction, uncertainty estimation, causal or treatment-effect prediction, and robustness under domain shift. -- We will evaluate the resulting models on real scientific prediction problems, such as biological response prediction, patient risk stratification, perturbation effect estimation, and data-limited biomedical decision support. The expected outcome is a new framework for building efficient, transferable, and reliable scientific foundation models. By reducing the need for repeated task-specific model training, this project aims to support faster hypothesis testing, better use of small scientific datasets, and more accessible AI tools for biology and biomedicine.</t>
         </is>
@@ -1669,40 +1795,45 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
           <t>51900</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Accelerating Multi-Agent Learning Through Advisor-Guided Value Transfer</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Carleton University</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>Accelerating Multi-Agent Learning Through Advisor-Guided Value Transfer</t>
         </is>
@@ -1716,40 +1847,45 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
           <t>51901</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Learning to Adapt: Opponent-Aware Fine-Tuning of Decentralized Multi-Agent Policies</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Carleton University</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>Learning to Adapt: Opponent-Aware Fine-Tuning of Decentralized Multi-Agent Policies</t>
         </is>
@@ -1763,40 +1899,45 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
           <t>51902</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Multi-Agent Reinforcement Learning for Safe and Efficient Autonomous Driving in Dense Traffic Scenarios</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Carleton University</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>Multi-Agent Reinforcement Learning for Safe and Efficient Autonomous Driving in Dense Traffic Scenarios</t>
         </is>
@@ -1810,40 +1951,45 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
           <t>51941</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Culturally Sensitive AI</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Université du Québec à Montréal</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>MONTREAL, Québec</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>During your internship, you will be involved in the development of machine/deep learning, sentiment analysis, speech transcription and information retrieval algorithms. Sub-field of artificial intelligence, machine learning studies and designs algorithms that learn from data to make predictions. You will apply your knowledge to tasks, questioning how AI-based systems could be designed to be culturally sensitive. You will have to handle large corpora of textual data to extract information, analyze their content, or discover embedded knowledge. You will explore various approaches (deep learning, genAI, etc.) to solve information extraction tasks, find relevant documents in a corpus, and classify documents (associate a category to a document), with a special focus on cultural adaptation. With our team, you will contribute to the development of automatic system that can, for instance, participate in evaluation campaigns like eRisk (https://early.irlab.org/) or CLPsych (http://clpsych.org/), or transcribe speech from languages spoken in various communities (see calame.tech).</t>
         </is>
@@ -1857,40 +2003,45 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
           <t>51840</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Geometric Machine Learning and Interaction of Large Medical Image Datasets</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>École Polytechnique de Montréal</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Geometric Machine Learning and Interaction of Large Medical Image Datasets</t>
         </is>
@@ -1904,40 +2055,45 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
           <t>51841</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Interactive Visualization and Manipulation of Modern Medical Images</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>École Polytechnique de Montréal</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>The complexity of modern medical imaging requires sophisticated visualization strategies. Through a combination of intelligent algorithms and advanced computer graphics, we reconstruct organs in 3D to ensure that physiological abnormalities can be efficiently identified. This internship focuses on developing a state-of-the-art visualization platform that integrates machine learning and image analysis. As a participant, you will master modern ML frameworks and innovative rendering techniques to build an interactive system capable of manipulating 3D and 4D (3D+t) datasets of the heart, brain, and other vital structures. As an intern, you will implement high-performance computer vision techniques to drive a robust retrieval and analysis system. You will join Team Polyshape at Polytechnique Montreal, a leading hub for engineering innovation. Our lab provides a vibrant, collaborative atmosphere with deep connections to premier research institutions across North America and Europe. Located in Montreal, you will experience a world-class cultural landscape in one of the most accessible and affordable major cities on the continent. Schedule and start dates remain flexible. Dates are flexible.</t>
         </is>
@@ -1951,40 +2107,45 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
           <t>51981</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Automated Software Modernization</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Concordia University</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>This research project focuses on developing automated approaches to modernizing legacy software systems using advanced software engineering and artificial intelligence techniques. Many existing systems rely on outdated architectures that limit scalability, security, and maintainability. The project aims to analyze legacy codebases, identify opportunities for refactoring, and transform monolithic applications into modular, cloud-native architectures. By leveraging tools for code analysis and machine learning-based pattern detection, the research will explore methods to reduce the complexity, cost, and risk associated with software modernization. The effectiveness of the proposed approaches will be evaluated using metrics such as performance, code quality, and system maintainability. The outcomes of this project are expected to contribute to more efficient and reliable modernization practices in both academic and industrial settings.</t>
         </is>
@@ -1998,40 +2159,45 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
           <t>52098</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Leveraging Large Language Models to Improve Software Development</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Concordia University</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>The research project focuses on the innovative application of large language models (LLMs) to assist in various aspects of software engineering. This project explores how LLMs can be integrated to improve software development processes, including but not limited to code generation, documentation, debugging, and testing. By leveraging the natural language understanding capabilities of LLMs, the project aims to provide tools that can interpret and generate human-like code comments, suggest code optimizations, and automate bug detection and resolution. This integration seeks to enhance developer productivity, reduce the complexity of software maintenance, and elevate overall code quality, ultimately contributing to more efficient and effective software development cycles.</t>
         </is>
@@ -2045,40 +2211,45 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
           <t>52508</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Computer Vision Methods for Surgical Navigation in Spine Surgery</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Université TÉLUQ</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>This project aims to develop an ultrasound-based surgical navigation solution to make spine surgery more accurate, safer, and more accessible. Each year, thousands of patients require spinal procedures involving the placement of pedicle screws to restore or maintain the biomechanical stability of the spine. However, inaccurate screw placement can lead to serious neurological, vascular, or mechanical complications. Current navigation approaches often rely on fluoroscopy or CT imaging, which can increase radiation exposure, require expensive equipment, and remain unavailable in many clinical settings. The goal of this project is to create and evaluate reliable ultrasound-based navigation methods that can support pedicle screw insertion during minimally invasive spine surgery. The project will combine ultrasound-to-3D model registration, automatic segmentation, adaptive planning, and real-time visualization of surgical instruments relative to patient anatomy. These methods will be integrated into an open-source surgical navigation platform, making the technology more accessible for research, training, and future clinical translation. A key scientific challenge will be to account for anatomical variability and biomechanical deformation during surgery, enabling robust registration between intraoperative ultrasound images and preoperative or patient-specific 3D models. The intern will contribute to the development, implementation, and evaluation of computer vision and image-guided surgery methods designed for realistic surgical conditions. The proposed approach will be quantitatively evaluated using ex vivo porcine spine models in minimally invasive pedicle screw insertion scenarios. Accuracy, robustness, repeatability, and usability will be assessed to determine the potential of the method as a radiation-free alternative to conventional navigation systems.</t>
         </is>
@@ -2092,40 +2263,45 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
           <t>52795</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>AI-Powered Autonomous Root Cause Analysis and Self-Healing Video Streaming Systems</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Concordia University</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>AI-Powered Autonomous Root Cause Analysis and Self-Healing Video Streaming Systems</t>
         </is>
@@ -2139,40 +2315,45 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
           <t>53165</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Mobile application assisting indoor navigation for people with visual impairments | L’application de téléphone cellulaire assistant la navigation intérieure pour les personnes malvoyantes</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Mobile application assisting indoor navigation for people with visual impairments | L’application de téléphone cellulaire assistant la navigation intérieure pour les personnes malvoyantes</t>
         </is>
@@ -2186,40 +2367,45 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
           <t>53166</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Anomaly detection in financial transactions using machine learning | Détection des anomalies dans les transactions financières par l’appentissage automatique</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Anomaly detection in financial transactions using machine learning | Détection des anomalies dans les transactions financières par l’appentissage automatique</t>
         </is>
@@ -2236,18 +2422,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2258,40 +2445,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>ID Proyecto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Universidad</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Campus</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Idioma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
@@ -2305,40 +2497,45 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
           <t>51202</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>LLM-Powered Intelligent Educational Systems</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>The deployment of artificial intelligence in online education systems has become very popular in recent years and recently published large language models (LLMs) tend to have a huge application potential on developing intelligent online education systems. This project is to develop and test a personalized online learning system where we will use LLM-powered AI systems like ChatGPT, Gemini, to generate knowledge graphs, personalized learning paths, to plan learning activities, and to conduct adaptive practicing and formative assessment.</t>
         </is>
@@ -2355,18 +2552,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2377,40 +2575,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>ID Proyecto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Universidad</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Campus</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Idioma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
@@ -2424,40 +2627,45 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
           <t>51212</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Soft Wearable Haptic Devices using Magnetic Actuation</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Advances in materials science, chemistry, mechanical engineering, and robotics engineering have brought soft actuators to interactive devices. A wide range of working principles have been used for developing soft actuators: pneumatics, hydraulics, electroactive polymers, acoustofluidics, electrorheological and magnetorheological fluids. However, current soft actuators possess several limitations which include: slow response, low/no force output, difficulty in precisely controlling them, or require high operating voltages with bulky control setups. Pneumatic actuators are commonly used in soft robotics because of their ability to generate large forces but they need high pressure, have low efficiency, are slow in response, and need noisy actuation valves. On the other hand, electrostatic actuators (e.g. dielectric elastomers) provide a high-frequency response but require thousands of volts with bulky control setups. This prohibits the use of these actuation principles in soft wearable settings. Recently electromagnetic actuation has been receiving a lot of attention because of its fast response, lower actuation voltage, and highly programmable and well-controlled movements. However, their deployment in interactive applications is not fully explored. Current state-of-the-art soft magnetic actuators in HCI are limited to low-resolution and enable only subtle vibration feedback. This project aims to develop high-resolution soft magnetic actuators that can deliver high force output and a variety of haptic sensations. By studying, simulating, and investigating novel device architectures, we aim to develop soft actuators that can be precisely controlled and programmed to open up new possibilities in AR/VR, Accessible computing, sports, and rehabilitation.</t>
         </is>
@@ -2471,40 +2679,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t>51330</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Behavioural Biometrics and the Hidden Risks of User Privacy Violations in Everyday Computing</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Behavioural Biometrics and the Hidden Risks of User Privacy Violations in Everyday Computing</t>
         </is>
@@ -2518,40 +2731,45 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
           <t>51940</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Artificial Intelligence for Sustainable Environment: Towards More Resilient Urban Forests</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Université du Québec à Montréal</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>MONTREAL, Québec</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Artificial Intelligence for Sustainable Environment: Towards More Resilient Urban Forests</t>
         </is>
@@ -2565,40 +2783,45 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
           <t>51158</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Secure LLM-Based Code Generation</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Concordia University</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2608,40 +2831,45 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
           <t>51306</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>High-performance practical blockchain systems</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>This is a multi-faceted project on improving core blockchain components in order to improve its performance. Students will be in charge of investigating one or more aspects of blockchains, formulating novel problems, designing, implementing, and evaluating their solution. The objectives of this project include the following. Note that students are expected to choose a subset of goals to fulfill: 1- Investigate relevant blockchain use cases in the public and private sectors, identify suitable blockchain platforms, and develop Proof-of-Concept applications. This includes: cryptocurrencies, NFTs, supply chain traceability, etc. 2- Develop and improve upon existing consensus algorithms, such as Proof-of-Work, PBFT, to support more peers, provide a higher transaction throughput, and deliver predictable commit times. 3- Improve the blockchain data structure (e.g., Merkle tree) for fast insertion, querying, and compressibility. Propose new blockchain structures (e.g., tree) with increased transaction parallelism. 4- Propose a data structure for storing off-chain information, with on-chain verification mechanisms, and a dynamic algorithm for offloading data. 5- Study the effect of networking on blockchain commit time, resilience to attacks, and fork rate. Develop networking protocols for enhanced performance. 6- Create blockchain middleware, delivering reusable services in a reliable and safe manner, such as messaging, identity management, replication, etc. 7- Integrate quantum technology to improve the security of blockchains, such as QRNG (quantum random number generation)</t>
         </is>
@@ -2658,18 +2886,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2680,40 +2909,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>ID Proyecto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Universidad</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Campus</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Idioma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
@@ -2727,40 +2961,45 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
           <t>51315</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Development of ReLiS a tool for conducting systematic reviews</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Université de Montréal</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>When a researcher wants to solve a particular problem, he first looks into the scientific literature (published papers) to see what exists on that subject. ReLiS is a tool that helps reduce the number of articles to analyze considerably (typically hundreds to thousands, depending on the topic of the study). ReLiS allows the user to define a systematic process to follow and to automate as many tasks as possible to researchers. When performing a systematic literature review, the researcher extracts information from each paper he reads so that he can observe trends on the subject and better characterize what has already been solved, and identify the next challenge. ReLiS is a generic framework for configuring, installing, and conducting systematic review projects. It offers statistical results on the data collected and on the process itself. ReLiS counts over 100 users world-wide, coming from a diversity of disciplines. It is open-source and available on GitHub. Our users continuously suggest improvements. There are many development projects available for improving ReLiS. These include, but are not restricted to: improving the user interface for large and small screens, adding technical features of a systematic review, automatically publishing the results of the review, automatically generating the documentation of the protocol followed.</t>
         </is>
@@ -2774,40 +3013,45 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
           <t>51796</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Interactive Visualization and Debugging of Software Engineering Agents</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Concordia University</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Large language models (LLMs) are now widely used across a broad range of domains and applications. More recently, advances in reasoning capabilities have enabled LLMs to operate as autonomous agents that tackle real-world tasks, such as resolving software repository issues and navigating graphical user interfaces through iterative planning, tool use, and dynamic runtime feedback. Despite this progress, LLM agents still struggle with complex long-context problems involving extended reasoning chains and multi-step interactions. In such cases, it becomes critical to identify which agent (who) made the mistake and at which step (when) the error was introduced. However, existing debugging workflows remain largely manual and lack effective interactive visualization and diagnostic tools for analyzing agent trajectories. This makes it difficult for developers to trace error propagation, inspect intermediate decisions, and understand how failures emerge over the course of long-horizon execution. In this project, we aim to design and implement an interactive system to support the visualization and debugging of AI agents.</t>
         </is>
@@ -2824,18 +3068,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2846,40 +3091,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>ID Proyecto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Universidad</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Campus</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Idioma</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
@@ -2893,40 +3143,45 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
           <t>53126</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Designing High-Performance Database Engines for Emerging Hybrid Workloads</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Designing High-Performance Database Engines for Emerging Hybrid Workloads</t>
         </is>
@@ -2940,40 +3195,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t>53669</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Investigate Teleportation Technique for Enhance Navigation in Complex Virtual and Augmented Reality Environment</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Investigate Teleportation Technique for Enhance Navigation in Complex Virtual and Augmented Reality Environment</t>
         </is>
@@ -2987,40 +3247,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>53677</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>From Ant to Giant: Comprehensible Teleportation Across Multiple Scales in Virtual Reality</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>From Ant to Giant: Comprehensible Teleportation Across Multiple Scales in Virtual Reality</t>
         </is>
@@ -3034,40 +3299,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>53787</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>User Interfaces for Software Tool Sharing and Discovery among Natural Scientists</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>User Interfaces for Software Tool Sharing and Discovery among Natural Scientists</t>
         </is>
@@ -3081,40 +3351,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>53791</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Large-scale Livestreamed Audience Participation Games</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Audience participation games (APGs) are games that allow spectators watching the game to participate in a way that also gives them an amount of meaningful impact on the game. There is recent interest in understanding how APGs can be designed specifically for livestreamed environments such as Twitch or Discord, as a break between normal stream content or to improve audience engagement. This project will explore potential interaction techniques and game mechanics for livestreamed APGs that enable a large number (100+) of spectators to participate in the game. We have an existing testbed environment developed in Unity that allows comparison of various game mechanics. The testbed is based on a style of game in which players work together to defeat a non-player boss character. This project will expand the testbed to support new game mechanics and and evaluate them with human participants.</t>
         </is>
@@ -3128,40 +3403,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>53890</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Evaluating Speech-Based Simulation Training for Aviation Communication</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Air Traffic Control (ATC) communication is a critical skill for aviation students and pilots. Students must listen accurately, use standardized phraseology, respond quickly, and follow correct communication protocols. However, opportunities for repeated low-stakes practice outside instructor-led role-play, simulator sessions, or aircraft time are limited. This project contributes to the development and evaluation of a free and open-source mobile application for aviation communication training. The ATC app presents realistic scenario-based exercises in which students listen to ATC instructions, respond verbally, and receive feedback on their performance. The first scenarios are based on Springbank Airport, which is used by Mount Royal University aviation students. Initial scenario types focus on taxi communication and runway-incursion prevention, since these are safety-relevant areas where communication errors can have serious consequences. The long-term goal is to support additional airports, flight schools, instructor dashboards, student progress tracking, scenario-authoring tools, and pilots seeking refresher practice. By summer 2027, the app is expected to have an initial working prototype and preliminary data collection. The Globalink student will help prepare the project for broader evaluation and future data collections. Possible tasks include processing exported student performance data, improving data structures for multi-turn scenarios, building dashboards to visualize learning trends, preparing anonymized research datasets, improving documentation, testing app workflows, and creating tools that help instructors or researchers interpret student performance. The project is interdisciplinary, involving computer science, aviation faculty, education researchers, statistics collaborators, and undergraduate research assistants. It is suitable for a student interested in software development, human-computer interaction, data analysis, learning analytics, or educational technology. The expected outputs include improved research infrastructure, data visualization tools, documentation, and contributions to an open-source aviation training platform.</t>
         </is>
@@ -3175,40 +3455,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>54340</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Full-Stack Deployment of a Web-Based Educational Game</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>We have developed a "Transition to Post-Secondary" game is aimed to prepare high school students with ADHD and Learning Disabilities with the knowledge to transition into university education. This web-based game consists of role playing and life simulation mechanics; learning elements regarding the university lifestyle are contained within the interactive segments of the game. The game features a narrative structure where the player makes friends with both staff and students to simulate an accurate university experience. The task for the Mitacs intern is to perform full-stack deployment of the game, setting up the game with a web-based log in system, front-end, and back-end database so that the game can be used by students from anywhere.</t>
         </is>
@@ -3222,40 +3507,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>54404</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>An open-source system for measuring chamber pressure in shooting sports</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Mount Royal University</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>An open-source system for measuring chamber pressure in shooting sports</t>
         </is>
@@ -3269,40 +3559,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>54461</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Towards Unified Explainable Machine Learning Models for Medical Image Analysis</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Towards Unified Explainable Machine Learning Models for Medical Image Analysis</t>
         </is>
@@ -3316,40 +3611,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>54463</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Resolution-agnostic Machine Learning Approaches for Medical Image Analysis</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>University of Calgary</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Calgary</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Calgary, Alberta</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Resolution-agnostic Machine Learning Approaches for Medical Image Analysis</t>
         </is>
@@ -3363,40 +3663,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
           <t>53328</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>PSGA: Compiler-Guided Retrieval-Augmented Generation for Correct and Scalable Parallelization of Scientific Computing Applications</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Concordia University of Edmonton</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>PSGA: Compiler-Guided Retrieval-Augmented Generation for Correct and Scalable Parallelization of Scientific Computing Applications</t>
         </is>
@@ -3410,40 +3715,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
           <t>53339</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Mobile Accessible Seamless Agent (MASA) Android App</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3453,40 +3763,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
           <t>53349</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Virtual Informal Personal (VIP) Chatbot Android App</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3496,40 +3811,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
           <t>53354</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>VIP Translator Android App</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3539,40 +3859,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
           <t>53364</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>VERAM: Verification-Oriented Evaluation of Retrieval-Augmented Methods for Trustworthy Scientific Code Generation</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Concordia University of Edmonton</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>VERAM: Verification-Oriented Evaluation of Retrieval-Augmented Methods for Trustworthy Scientific Code Generation</t>
         </is>
@@ -3586,40 +3911,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
           <t>53372</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Memorize book reading Android App based on GAIOLA</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3629,40 +3959,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
           <t>53419</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>mFieldtrip application development with RAG-Chatbot</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>This project aims to upgrade an open mobile application used for a self-guided field course in physical geography. The field course involves real excursions across Alberta, where students are guided by a mobile application in the absence of direct instructor supervision. The app supports learning by drawing students’ attention to key geographical features and providing associated instructional content and field-based activities. The project will require the student to use a cross-platform development environment, such as Flutter, to develop and enhance the mFieldtrip mobile application (iOS/Android). Advanced features will be implemented using up-to-date technologies, including data analytics, optical character recognition (OCR), and field-based tools to support data collection and analysis. In addition, the project will focus on finalizing the mobile application by enhancing usability and refining the user interface design to improve accessibility, intuitiveness, and overall user experience, ensuring the app is both easy and pleasant to use in real field conditions.</t>
         </is>
@@ -3676,40 +4011,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
           <t>53467</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Generative AI supported Visualized Information Personal (VIP) Reading/Reader Android App</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Generative AI supported Visualized Information Personal (VIP) Reading/Reader Android App</t>
         </is>
@@ -3723,40 +4063,45 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
           <t>53471</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Driving and Walking Navigation Android App built on Open Street Map and Next-Stop Recommender</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>Driving and Walking Navigation Android App built on Open Street Map and Next-Stop Recommender</t>
         </is>
@@ -3770,40 +4115,45 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
           <t>53472</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Generative AI supported Next Stop Recommender Android App</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Athabasca University</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Alberta</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Edmonton, Alberta</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>The project is enhancing the following existing research VIP Research Group (https://www.youtube.com/@vipresearchgroup) has: - Next Stop Recommender (https://nextstop.vipresearch.ca/) which can provide users recommendation for their next visit according to the similarity of their behaviours between each others and the connections amongst locations. - he Generative AI (GenAI) supported Note Takers App (https://notetakers.vipresearch.ca) is an innovative tool designed to help users capture and organize notes from spoken conversations, incorporates Public Key Infrasture (PKI), Secure Sockets Layer (SSL) and salted secured hash algorithm. The research project involves three parts: (1) The production server needs to (a) have Open Street Map Tile Server and Routing Server for selected countries and regions; (b) offers endpoints that allows client apps (including the Android App) to download selected region's map; (c) receive the requests for synchronizing users their historical records, preferences and app's configuration anonymously in a secure and privacy protected way; (d) allow administrators to test new Text-Generation, Speech-to-Text, and Text-to-Speech (TTS) GGUF models and auto update available model list and corresponding voice options (for TTS models); (e) offers endpont for accessing server-side services on Text-Generation and Speech-to-Text. (2) The Android App allows users to (a) download an available Text-Generation, Speech-to-Text, and Text-to-Speech (TTS) GGUF model from the production server according to the available model list provided by the endpoint; (b) choose pre-downloaded models and a supported voice from the selected TTS model; (c) ask the app to recommend places to visit for next via talking to the app with natural language; (d) listen to the app to explain the recommendations; (e) use the endpoint the production server offers to synchronize device uuid, corresponding configurations, and historical records anonymously in a secure and privacy protected way. The app can take NoteTakers' secure communication workflow and design as reference (see https://maiga.athabascau.ca/#notetakers and https://notetakers.vipresearch.ca).</t>
         </is>
@@ -3817,40 +4167,45 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
           <t>53534</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Understanding LLM Reasoning Unfaithfulness</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Large language models often produce step-by-step "reasoning" before giving an answer, and users increasingly trust these explanations. But a model's stated reasoning may not reflect what actually drove its answer. It can rationalize after the fact, hide the cues it truly relied on, or be steered by signals it never mentions. This gap, known as reasoning unfaithfulness, is a serious problem for safety, trust, and oversight of modern AI. This project investigates when and why LLM reasoning becomes unfaithful. The student will design controlled experiments that probe whether a model's chain-of-thought genuinely explains its behavior, measure faithfulness across tasks and model families, and explore how factors like post-training and adversarial manipulation affect it. The work combines hands-on experimentation with open-source models, careful evaluation design, and analysis of results. The intern will gain experience in trustworthy machine learning, LLM evaluation, and research methodology and contribute to findings suitable for a workshop or conference submission.</t>
         </is>
@@ -3864,40 +4219,45 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
           <t>53734</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Efficient Training of Diffusion Models</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Carleton University</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>This project aims to develop novel optimization objectives that accelerate the training and inference of diffusion models. While modern diffusion models can achieve high-fidelity data generation, their reliance on lengthy denoising chains imposes prohibitive computational costs. Recent developments on temporal consistency show promising results without incurring a high computational cost. By designing alternative loss functions that leverage geometric shortcuts, this research seeks to reduce the number of training and inference steps for diffusion models. This project aims to develop general objectives for various diffusion architectures, making them more computationally viable for resource-constrained applications.</t>
         </is>
@@ -3911,40 +4271,45 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
           <t>53930</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Feature Selection for High Dimensional imbalanced Problems</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Feature selection methods are essential to deal with high dimensional tasks. In this project, we will tackle the problem related with high dimensional imbalanced problems. To address this problem, we will implement and test standard feature selection methods, and novel feature selection methods developed for high dimensional imbalanced problems. The main goal is to develop a novel feature selection method that is suitable for high dimensional problems that also suffer from class imbalance. The key idea is to take into account the relation between the features and the classes, especially the minority one in order to prevent a performance degradation in this class.</t>
         </is>
@@ -3958,40 +4323,45 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
           <t>53931</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Multi-Task Active Learning</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>In many real-world predictive problems, the available data has frequently a vast majority of instance unlabelled while only a small number of instances is labelled. This happens because the labeling process is often both expensive and difficult, requiring an expert or a team of experts to do the job. Active learning is a strategy that allows us to select the most useful cases to be labelled by experts. Ideally, the selected cases should be the ones that will benefit the more the learning algorithm that is being used. Another important aspect of these data sets is the fact that in some situations the same data can be used for multiple prediction problems, i.e., the same data set can be used to obtain the predictions for several tasks. For instance, a data set with movies reviews, can be used to predict the movie genre, the number of stars it will reach or the profit it will generate. In this project our main goal is to address the multi-task problem in a semi-supervised context through the application of active learning. We will start by implementing and testing basic active learning independent methods for each predictive task. A consensus will be derived to decide for which cases a label will be obtained. Then, we will proceed with the implementation of experiments for comparing the performance of: i) this baseline strategy; alternative ways for obtaining the consensus through weights; and the combination of basic selection strategies with outlier detection and resampling methods. This project main outcomes are: - the development of novel solutions for the multi-task active learning problem; - the experimental comparison of of several alternative solutions; - a report in the form of a research paper describing the algorithms proposed and main results.</t>
         </is>
@@ -4005,40 +4375,45 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
           <t>53935</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Deep Learning for Imbalanced Data</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>Deep learning has gained a vast popularity. These methods are nowadays applied across different applications and domains. Still, the relation between the use of deep learning methods in imbalanced problems is under-explored. The main goal of this project is to investigate this relation, with a special focus on the complexity of the trained models. We will set up experiments to observe the impact of applying deep learning models under problems with different imbalance ratios and different task complexities (class overlap, small disjunct, high dimensionality, etc...). We will aim at understanding the impact of the imbalance and other characteristics in the performance of these models considering different model architectures and complexity.</t>
         </is>
@@ -4052,40 +4427,45 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
           <t>54076</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Decision-focused Learning for Distributed Energy Resource Optimization</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>Modern power systems are facing increasing uncertainty from both the supply side, due to the integration of renewable energy, and the demand side, due to emerging large energy consumers such as AI-focused data centers. These uncertainties complicate the control and optimization of energy resources, where system operators need to predict uncertain quantities and then make operational decisions based on the predicted parameters. A commonly adopted approach treats prediction and optimization as two separate stages: first, a machine learning model is trained to predict unknown parameters from observed features; then, an optimization problem is solved using the predicted parameters. However, machine learning predictions are rarely perfect, and prediction errors can propagate to the downstream optimization problem, leading to suboptimal or risky decisions. To address this challenge, this project explores decision-focused learning, an end-to-end paradigm that learns predictive models in a way that is directly informed by the loss of the downstream optimization task. We will study decision-focused learning for the optimization of distributed energy resources (DERs), such as battery storage and electric vehicles. We will start with a storage arbitrage problem, where a grid-scale energy storage operator predicts electricity prices and determines charge/discharge decisions to maximize profit while accounting for prediction errors and financial risk. We will first apply standard decision-focused learning to this problem and compare its performance with the conventional two-stage approach that considers prediction and optimization separately. Next, we will incorporate uncertainty quantification into decision-focused learning by leveraging calibrated uncertainty estimates in a downstream robust optimization problem, with the goal of further controlling risk in storage arbitrage. Building on these approaches, we will further study DER management problems that involve uncertain renewable generation and uncertain consumer demand. The goal is to reduce operational costs of DERs while explicitly accounting for uncertainty and risk.</t>
         </is>
@@ -4099,40 +4479,45 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
           <t>54161</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Energy Storage-Assisted Scheduling under Grid Capacity Constraints</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>University of Ottawa</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>The rapid growth of large energy consumers, such as AI data centers and electric vehicle charging fleets, is creating new operational challenges for power grids. These loads can be large, time-varying, and highly concentrated, while grid capacity expansion is often slow, costly, and constrained by planning and permitting processes. As a result, limited grid capacity may become a major barrier to the timely deployment of large energy-consuming infrastructures. This project studies how energy storage can be co-optimized with large energy consumers to reduce grid capacity requirements and lower electricity costs. The key idea is to use storage as a flexible resource: it can be charged during periods of low system demand or low electricity prices, and discharged during peak-demand periods. In this way, storage can smooth the net load seen by the grid, reduce peak power draw, and improve the economic operation of the system. We will first formulate the optimal scheduling problem for energy storage under given grid capacity, demand profiles, storage constraints, and electricity prices. This offline optimization model will provide a benchmark for evaluating system performance and understanding the value of storage. Building on this formulation, we will develop real-time scheduling methods, including model predictive control, to handle uncertain and time-varying demand and prices. The proposed methods will be evaluated using real-world data traces. The goal is to develop practical optimization tools for storage scheduling and capacity planning that support the cost-effective and scalable deployment of large energy-consuming infrastructures under grid capacity constraints.</t>
         </is>
@@ -4146,40 +4531,45 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
           <t>54217</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Conversational AI for Older Adults</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Carleton University</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Ottawa</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>Ottawa, Ontario</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>Older adults face increasing barriers to digital participation. Conversational agents powered by artificial intelligence (AI), such as ChatGPT, Google Gemini, and Microsoft Copilot, are transforming the way people gather information, learn, and support their well-being. However, these systems are rarely designed to be inclusive of the needs of older adults (people 60+ years old), especially for their on-the-go, context-aware use. This research addresses these issues through the development of conversational AI agents that integrate contextual information with large language models to provide on-the-go, just-in-time assistance for older adults. These systems can be life changing and enable a new level of independence for older adults, especially those with disabilities such as mild cognitive impairment, mobility issues, or vision loss, at a more accessible price point when compared to existing smart home alternatives (e.g., through purchasing one system instead of multiple peripherals that must be installed around a smart home). This research sits at the intersection of user experience design, digital inclusion, aging, and technology. Aspects core to the project include inclusive design, accessibility, iterative design, and design thinking. The application will first start as a preliminary prototype and refined through several iterations into a developed application. The created application will be evaluated with stakeholders, including older adults, their caregivers, and members of the project team. Evaluation criteria will include but not limited to: usability, accessibility, inclusiveness, acceptability, and user perceptions. No prior work has explored integrating wearable computer vision systems into conversational AIs for inclusive aging support. Thus, conversational agents embedded in wearables (e.g., smart glasses) will be the primary focus of this project, but this may change depending on evolving needs of the project and users.</t>
         </is>
@@ -4193,40 +4583,45 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
           <t>51231</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Expressive Interaction with AI</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Université de Montréal</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Interacting with an AI, such as a large language model (LLM), is typically done through textual prompts in a chat-like interface. While easy to use, this interaction is often slow and ambiguous. This is particularly true when AI is used to help with creative tasks such as drawing or writing. In this project, we aim to explore alternative ways of interacting with AI. Examples include the use of digital instruments, gestural interaction, or even sketching. Specifically, the idea would be to understand the needs of creative professionals (e.g., artists, writers, and even programmers) and to develop tools to support their work. Feel free to check out examples of such interactions developed in my research group: https://damienmasson.com/pdfs/directgpt.pdf and https://damienmasson.com/pdfs/textoshop.pdf.</t>
         </is>
@@ -4240,40 +4635,45 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
           <t>53509</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Code in artist's social media</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Université de Montréal</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Generative artists write code, run code, tweak code in order to generate artworks. Many artists share the artworks on online platforms, such as instagram or bandcamp. Sometimes, artists also share the code. Sharing code can have mutliple meanings: cool medium, transparency, generosity, traceability. Sharing code can take several forms, such as posting a link to a code repository along a social media post, sharing a picture or screencast of the code that performs the artworks, or it might be that the act of writing code is part of the artistic performance. In this project, the student will develop novel methods to collect source code that is shared on social media platforms. The goal is to explore these different practices of artistic code sharing as well as the different motivations of artists for sharing code. https://spectrum.library.concordia.ca/id/eprint/992759/1/Thow_MA_F2023.pdf https://www.google.com/search?q=%22github.com%22+site%3Abandcamp.com https://youtu.be/ca7xzqR7WaY</t>
         </is>
@@ -4287,40 +4687,45 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
           <t>53511</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Full stack software specialization</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Université de Montréal</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Software applications depend on a large number of dependencies: third-party libraries that provide reusable features, language standard libraries, containers that provide reproducible environments for release and distribution. This vast network of dependencies forms the software supply chain of the application. This software supply chain provides all the benefits of software reuse: share development of generic features, reduction of development time. Yet, it also introduces challenges regarding reliability, security and performance. A key part of these challenges comes from the fact that all reused components are generic so they can be reused in many different contexts, but a specific application uses only a fraction of each reused component. In this internship, the student will investigate opportunities to specialize the software supply chain of an application at different levels of the stack (libraries, standard library and container). This will involve static and dynamic code analysis to determine which parts of the software supply chain are used, as well as code transformation to specialize the supply chain. https://arxiv.org/pdf/2302.08370 https://dl.acm.org/doi/pdf/10.1145/3274694.3274703 https://www.usenix.org/system/files/raid20-ghavamnia.pdf</t>
         </is>
@@ -4334,40 +4739,45 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
           <t>53517</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Niche code sharing platforms</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Université de Montréal</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>The vast majority of public source code is hosted on Github. Yet, there exists many alternative to host and share source code, such as codeberg, Gitea, sourcehut, or forgejo. These alternatives are niche and mostly used by contributors who explicitly seek alternatives to Github. These motivations can be autonomy, independence, subversion, cultural artistic. In this internship, we study the open source communities who turn to these alternative, niche, code hosting platforms. We mix code analysis, text analysis and interviews, to categorize the types of projects that are hosted on these platforms, as well as the motivations of the contributors and communities. https://dl.acm.org/doi/pdf/10.1145/2702123.2702549 https://fupress.org/journal/JSCADD/index.php/journal/article/download/63/27 https://www.reddit.com/r/foss/comments/1mpf69k/codeberg_sourcehut_or_other/</t>
         </is>
@@ -4381,40 +4791,45 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
           <t>53546</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Building Trustworthy Digital Twins with LLMs and Formal Methods</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>École Polytechnique de Montréal</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4424,40 +4839,45 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
           <t>53948</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Multimodal Large Language Models for document understanding</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>This project aims to develop multimodal large language models (MLLMs) capable of understanding, interpreting, and reasoning over complex documents that combine text, images, tables, charts, and diagrams. Rather than training foundation models from scratch—which would require prohibitive amounts of data and computational resources—the project will focus on efficiently adapting and fine-tuning existing state-of-the-art MLLMs for document understanding tasks. Particular emphasis will be placed on parameter-efficient adaptation methods, reducing annotation requirements through self-supervised and weakly supervised learning, and improving model efficiency. Applications include scientific literature analysis, technical documentation, administrative and legal document processing, and intelligent information retrieval systems.</t>
         </is>
@@ -4471,40 +4891,45 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
           <t>53958</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Emotion Recognition with Multimodal Large Language Models</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>This project aims to develop methods for recognizing human emotions using multimodal large language models (MLLMs) that can jointly process and reason over multiple sources of information such as facial expressions, speech, text, and contextual signals. The goal is to move beyond single-modality emotion recognition by leveraging the complementary nature of different modalities to obtain more robust and accurate predictions. Rather than training models from scratch, the project will focus on adapting and fine-tuning existing multimodal foundation models to emotion understanding tasks, making use of parameter-efficient learning strategies and limited labeled data. A key challenge is to effectively align and fuse heterogeneous signals (e.g., visual cues from facial expressions, acoustic features from voice, and semantic information from language) into a coherent representation of emotional state. The resulting models are expected to improve performance in real-world, noisy, and unconstrained environments, with applications in human-computer interaction, affective computing, mental health monitoring, and user behavior analysis.</t>
         </is>
@@ -4518,40 +4943,45 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
           <t>53960</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Efficient Autoregressive Generative Modelling</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>École de Technologie Supérieure</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
       <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>This project focuses on improving autoregressive generative models for image synthesis, with a particular emphasis on how images are represented and encoded into discrete tokens. Autoregressive models generate images token by token, but their effectiveness strongly depends on the quality and efficiency of the underlying tokenization process. The main goal of this project is to design more efficient and informative visual token representations that reduce redundancy while preserving semantic and structural content. This includes investigating improved image token encoders, more compact discrete representations, and alternative ways of organizing visual information for autoregressive modeling. A key objective is to reduce computational cost and sequence length during both training and inference, while maintaining or improving image generation quality. The project will explore methods such as learned visual tokenizers, compression-aware representations, and structure-preserving encoding schemes. The resulting methods aim to make autoregressive image generation more efficient and scalable, enabling higher-quality synthesis with reduced computational resources.</t>
         </is>
@@ -4565,40 +4995,45 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
           <t>53991</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Verified Concurrent Algorithms</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Université du Québec à Montréal</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Montréal</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>The MOST programming language (Kavanagh and Pientka, 2024) extends traditional session-typed languages with concurrent type-level computation to more precisely specify communication protocols. In particular, protocols specifications are very restricted concurrent programs that generate a communication protocol based on past communications in a system. MOST users write both a program and its protocol specification, and MOST's type system ensures that the program respects its specification. This project will use MOST to specify and verify concurrent algorithms and data structures, including stacks, queues, and concurrent hash-tries. Since concurrent algorithms and data structures are often described in terms of shared memory, they will need to be redesigned to be implemented as a collection of interacting processes. We will draw inspiration from the literature and from open-source software projects to produce other case studies. These case studies will inform future development of MOST, form a reusable library of verified concurrent algorithms, and help develop principles for specifying concurrent algorithms and data structures in this setting.</t>
         </is>
@@ -4612,40 +5047,45 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
           <t>54048</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>EN: Artificial intelligence methods to automate video surveillance in metro stations \ FR: méthodes d'intelligence artificielle pour automatiser la vidéosurveillance dans les stations de métro</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Université TÉLUQ</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Québec</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Montreal, Québec</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>Either English or French</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>EN: Artificial intelligence methods to automate video surveillance in metro stations \ FR: méthodes d'intelligence artificielle pour automatiser la vidéosurveillance dans les stations de métro</t>
         </is>
